--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,417 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1804400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1761800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1758500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1766200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1707600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1654800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1635500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1786700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1417600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1416800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1209600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1090600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1017500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1019400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1187300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1179800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1208300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1153600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1203100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1183500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1178900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1146500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1143400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E9" s="3">
         <v>166000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>229200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>226000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>260900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>161400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>193200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>208100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>162000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>53500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>59000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>39200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>75300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>51200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>52200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>94700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>44100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>65200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>91700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>125900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>84800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>103300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>132500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>141200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>137800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>136300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>122400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>143300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1669200</v>
+      </c>
+      <c r="E10" s="3">
         <v>1595800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1529300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1540200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1446700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1493400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1442300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1578600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1255600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1363300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1150600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1051400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>942200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>968200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1135100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1085100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1121400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1109500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1137900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1091800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1053000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1061700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1040100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>997300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,192 +1299,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-563800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-645500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-11100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>5200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>21900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2749700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>146000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>153000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>126300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>53200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>118500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1015800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>98800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>22500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>16100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>31200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>15300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>45600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>9900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>631400</v>
+      </c>
+      <c r="E15" s="3">
         <v>623000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>615600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>610500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>593700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>580900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>580700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>634400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>555800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>393400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>392200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>396600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>401800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>416000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>411800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>415800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>415900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>415300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>419100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>425800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>425900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>412700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>417700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>422700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>425400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>428300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>435000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>438500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>433500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>324800</v>
+      </c>
+      <c r="E17" s="3">
         <v>255500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>953500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>970400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>951700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>864400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>900800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3689600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>983100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>668000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>650500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>546300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>659300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1543900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>615700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>597600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>590200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>555300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>566700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>589500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>637800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>573800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>620300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>643100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>673200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>695700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>666000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>654300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>693300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1479600</v>
+      </c>
+      <c r="E18" s="3">
         <v>1506300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>805000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>795800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>756000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>790400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>734700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>434500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>748800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>559100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>544300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>358200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-524500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>571600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>582200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>618100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>598300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>636400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>594000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>541100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>572700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>523100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>486700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>541300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>514500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>528200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>535200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>616600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,468 +1748,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E20" s="3">
         <v>119300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>160600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>108800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>123700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>61400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>22700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>39800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-121200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>21800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>45800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>107400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>37100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>68400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>19900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>55800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>105900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>51900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>61700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>60500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>40800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>77200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2214300</v>
+      </c>
+      <c r="E21" s="3">
         <v>2248700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1581200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1515100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1473300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1432800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1338200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1017500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1181900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>973700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>943100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>745000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-229700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1005200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1043800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1141400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1050800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1123800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1025500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>989500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1013000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1001000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>495900</v>
+      </c>
+      <c r="E22" s="3">
         <v>447000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>427400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>436200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>420300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>390800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>380800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>369500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>287200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>292900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>280800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>310500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>307300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>309700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>306100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>374900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>308900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>322600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>318300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>301800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>297000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>289400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>291000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>274900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>278200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>266000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>279200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>271300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1087000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1178700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>538200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>468300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>459300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>461100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>357500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>92200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>501300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>288700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>265800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>32700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-953000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>283700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>321900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>350600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>326500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>382100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>281400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>259200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>300700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>289500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>301600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>318300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>298000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>322700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>296800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>422600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E24" s="3">
         <v>110700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>75700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>65600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>50000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-278300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-106100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>38300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>43500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>39000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>42400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>49700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>36600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>39100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>34200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>42000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>38600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>60700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1047900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1068000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>462500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>402700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>459500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>396800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>307400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>439200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>248200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>225900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>25600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-846900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>245400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>278500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>311600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>284100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>332500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>244800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>231000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>261600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>251900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>262400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>290300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>263900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>280800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>258300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>361900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1105800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1105300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>492900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>432100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>495000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>440000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>339800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>88800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>433900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>249800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>228000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-849900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>246100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>276800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>309800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>270300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>331500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>234200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>232600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>263400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>254200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>265400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>288300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>265800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>282900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>261200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>364700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2600,8 +2660,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2618,11 +2678,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2636,8 +2696,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2886,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-103200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-119300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-160600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-108800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-123700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-61400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-22700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-39800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>121200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-21800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-45800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-107400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-37100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-68400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-19900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-55800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1105800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1105300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>492900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>432100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>495000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>440000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>339800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>88800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>433900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>249800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>228000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-849900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>246100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>276800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>309800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>270300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>331500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>234200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>232600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>263400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>254200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>265400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>266300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>265800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>282900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>261200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>364700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1105800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1105300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>492900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>432100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>495000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>440000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>339800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>88800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>433900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>249800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>228000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-849900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>246100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>276800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>309800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>270300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>331500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>234200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>232600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>263400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>254200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>265400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>266300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>265800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>282900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>261200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>364700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1627200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2415300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1153900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1089000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1597100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1098500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1229000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1185700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1728800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1311200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1402900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1447500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1248800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3244400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2382700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4693900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1121400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1036900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>782900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2348100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1204000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1176000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1598500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,129 +3626,135 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>566700</v>
+      </c>
+      <c r="E43" s="3">
         <v>538000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>561500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>624300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>593300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>487100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>469400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>567100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>636500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>647200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>525400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>349000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>343200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>428900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>419800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>279200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>403400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>330400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>276000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>241200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>260700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>335500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>266700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>286000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>425800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>301900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>259600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>218100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>253700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E44" s="3">
         <v>76800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>72600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>59200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>55900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>43000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>53400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>51900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>48600</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
@@ -3676,145 +3771,151 @@
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="R44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
         <v>3200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>57200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>20300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>31000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>55000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>37100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>37000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>39000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>42300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>46900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>59400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>52700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4268700</v>
+      </c>
+      <c r="E45" s="3">
         <v>4592000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4467500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4709300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4522400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5346400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5234800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5056500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5039100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2070100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2078600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2421700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2237200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2800500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3465400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3212200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3052900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3012300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3038300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3069700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3104300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3400300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3241800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3905,284 +4006,296 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3631600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3438900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3288200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2972600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3067400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3630300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3732400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3859700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2994700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1443300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1506000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1578100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1545700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1631300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1728600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1276600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1222600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1247600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1187800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1181300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1194400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1194800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1214800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>974200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>916700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>898000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57148200</v>
+      </c>
+      <c r="E48" s="3">
         <v>56298000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55675500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55563100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55302800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54751400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54433800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54686500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57946300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34465600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34797100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34626000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35219600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34799600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35422400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35738700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35940500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35303800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35329900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35159700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35081500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33215800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32977000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2893100</v>
+      </c>
+      <c r="E49" s="3">
         <v>3021000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3151900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3334900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3549700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3800700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3974100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4118300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4653400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>802300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>828200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>850000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>874500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>912900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1031500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1076100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1117000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1230000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1276200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1381400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1441800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1528600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1617300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>770700</v>
+      </c>
+      <c r="E52" s="3">
         <v>813400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1177800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>996900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>662800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>267800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>347200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>439800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>611900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>537500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>368000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>399900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>378100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>390400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>513200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>626300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>610600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1113800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>846300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1002600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>533400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>827300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>656000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>747400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>735900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>652000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71274600</v>
+      </c>
+      <c r="E54" s="3">
         <v>71593700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>69928400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69684400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69726900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69811200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69747600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70208200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74569800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>41499300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41824100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>42065000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42048000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>44421100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>45193800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47144800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>43749200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43549000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43067900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44717000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43208900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>42149500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>42019400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,100 +4838,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>444000</v>
+      </c>
+      <c r="E57" s="3">
         <v>430000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>475300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>582000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>475200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>711100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>730700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>750800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>850200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>263600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>281300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>243700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>222200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>223100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>220100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>240400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>239100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>233400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>245800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>272000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>294300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>274900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>283900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>303900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>307400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>288100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>295500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>302400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>330400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4848,23 +4981,23 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>11700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9000</v>
-      </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
@@ -4875,8 +5008,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -4893,100 +5026,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4323100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4134200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3889700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3814400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3782000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3535700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3578300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3512900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4200400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2329700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2566800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2650700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2670700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2697700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2876000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3186500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3244500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3336800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3326300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3413000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3268700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3363100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3314500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5077,192 +5216,201 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46483900</v>
+      </c>
+      <c r="E61" s="3">
         <v>47492800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46255800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46295900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46533000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>47350100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47927900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>48912900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>50204700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>27539700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>28098600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28553100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28742100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31087100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30683900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>32760800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>29474500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29280000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29014200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>30750100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29507600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>28387500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28545500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2526100</v>
+      </c>
+      <c r="E62" s="3">
         <v>2444000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2333900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2260000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2194100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1925700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1859500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1807600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2085200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1054900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>996000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>954000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>913400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>884100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>990300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>950200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>910300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>935800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>892200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>842100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>804600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>789900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>750500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>712400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>673900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>685900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>655900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>615300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>579000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54685700</v>
+      </c>
+      <c r="E66" s="3">
         <v>55300000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53616500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53639000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53609400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54243500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54713200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55555100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>57999000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>31644400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>32440600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32925600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>33183600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>35609700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35559800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>37761900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>34434300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34374100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34054900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35810800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34380900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33279700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33349900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10802600</v>
+      </c>
+      <c r="E72" s="3">
         <v>9703300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8598000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8104800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7674900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7181000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6741800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6408100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8410300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8322600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7888700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7625700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7399700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7380700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8232500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7986100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7734600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7424100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7157200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6825300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6591700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6359700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6096000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16588800</v>
+      </c>
+      <c r="E76" s="3">
         <v>16293700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16311900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16045400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16117500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15567700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15034400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14653100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16570700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9855000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9383500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9139300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8864500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8811400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9634000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9382900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9314900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9174900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9013000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8906200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8828000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8869900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8669500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1105800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1105300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>492900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>432100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>495000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>440000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>339800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>88800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>433900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>249800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>228000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-849900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>246100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>276800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>309800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>270300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>331500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>234200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>232600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>263400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>254200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>265400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>266300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>265800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>282900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>261200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>364700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7003,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>631400</v>
+      </c>
+      <c r="E83" s="3">
         <v>623000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>615600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>610500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>593700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>580900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>580700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>634400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>555800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>393400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>392200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>396600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>401800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>416000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>411800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>415800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>415900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>415300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>419100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>425800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>428500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>415300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>422100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>425500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>428200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>431000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>438900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>442800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>438200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1399600</v>
+      </c>
+      <c r="E89" s="3">
         <v>1305200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1193200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1363400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1550600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1111900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1171900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1336600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1734500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>787800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>771200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>400400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>652500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>541000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>307900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>628900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>768300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>817100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>774500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>745700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>778400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>716700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>607300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>738000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>724300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>817200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>797200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>801500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>935200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1580200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-944700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-685000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-975800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-312900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-19500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-99100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-146100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-98600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-61300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-354100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-436100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-298900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-280300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-406700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-637200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-420300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-628600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-303100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-973200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-453600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-844200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-216100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-646600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-187300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-302600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>69300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-220800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>70000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-326200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-235200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-714600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-910900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-546100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-783200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-718900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8118,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8211,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1554600</v>
+      </c>
+      <c r="E100" s="3">
         <v>289000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-166500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-579700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-403700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-897800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>21683500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-660400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-550600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-288700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>270100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3189500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>48700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>321700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1197100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>965800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-93700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-484500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>212800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>928800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="J101" s="3">
-        <v>500</v>
       </c>
       <c r="K101" s="3">
         <v>500</v>
       </c>
       <c r="L101" s="3">
+        <v>500</v>
+      </c>
+      <c r="M101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-781200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1289700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>53300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-493100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>500100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-145700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>56200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-568500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>380200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-58900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-82100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>180200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>882700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3582200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>103700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>226300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1159200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-449700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-593700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>428000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>205400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1858500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1804400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1761800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1758500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1766200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1707600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1654800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1635500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1786700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1417600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1416800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1209600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1090600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1017500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1019400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1187300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1179800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1208300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1153600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1203100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1183500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1178900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1146500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E9" s="3">
         <v>135200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>166000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>229200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>226000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>260900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>161400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>193200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>208100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>162000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>53500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>75300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>51200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>52200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>94700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>86900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>44100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>65200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>91700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>125900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>84800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>103300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>132500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>141200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>137800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>136300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>122400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>143300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1709900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1669200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1595800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1529300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1540200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1446700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1493400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1442300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1578600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1255600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1363300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1150600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1051400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>942200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>968200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1135100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1085100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1121400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1109500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1137900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1091800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1053000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1061700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>997300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,8 +1125,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1221,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,198 +1319,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-20100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-563800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-645500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-11100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>21900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2749700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>146000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>153000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>126300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>53200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>118500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1015800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>98800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>22500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>16100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>31200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>17800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>15300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>10400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>45600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>9900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>633500</v>
+      </c>
+      <c r="E15" s="3">
         <v>631400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>623000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>615600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>610500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>593700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>580900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>580700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>634400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>555800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>393400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>392200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>396600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>401800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>416000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>411800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>415800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>415900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>415300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>419100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>425800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>425900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>412700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>417700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>422700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>425400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>428300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>435000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>438500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>433500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>881300</v>
+      </c>
+      <c r="E17" s="3">
         <v>324800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>255500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>953500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>970400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>951700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>864400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3689600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>983100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>668000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>650500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>546300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>659300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1543900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>615700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>597600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>590200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>555300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>566700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>589500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>637800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>573800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>620300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>643100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>673200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>695700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>666000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>654300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>693300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>977200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1479600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1506300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>805000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>795800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>756000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>790400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>734700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>434500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>748800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>559100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>544300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>358200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-524500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>571600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>582200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>618100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>598300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>636400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>594000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>541100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>572700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>523100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>486700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>541300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>514500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>528200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>535200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>616600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,483 +1782,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E20" s="3">
         <v>103200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>119300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>160600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>108800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>123700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>61400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>22700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>39800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>22500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-121200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>21800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>45800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>107400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>37100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>68400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>19900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>55800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>105900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>51900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>61700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>60500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>40800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>77200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1783800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2214300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2248700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1581200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1515100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1473300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1432800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1338200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1017500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1181900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>973700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>943100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>745000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-229700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1005200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1043800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1141400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1050800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1123800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1025500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>989500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1013000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>491500</v>
+      </c>
+      <c r="E22" s="3">
         <v>495900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>447000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>427400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>436200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>420300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>390800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>380800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>369500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>287200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>292900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>280800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>310500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>307300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>309700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>306100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>374900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>308900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>322600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>318300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>301800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>297000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>289400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>291000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>274900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>278200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>266000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>279200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>271300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>658800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1087000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1178700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>538200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>468300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>459300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>461100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>357500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>92200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>501300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>288700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>265800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>32700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-953000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>283700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>321900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>350600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>326500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>382100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>281400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>259200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>300700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>289500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>301600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>318300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>298000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>322700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>296800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>422600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E24" s="3">
         <v>39000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>110700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>75700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>65600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>50000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-278300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>62100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-106100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>38300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>43500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>49700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>36600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>28100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>34200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>42000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>38600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>60700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>564700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1047900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1068000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>462500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>402700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>459500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>396800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>307400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>72100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>439200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>248200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>225900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>25600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-846900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>245400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>278500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>311600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>284100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>332500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>244800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>231000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>261600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>251900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>262400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>290300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>263900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>280800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>258300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>361900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>604200</v>
+      </c>
+      <c r="E27" s="3">
         <v>1105800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1105300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>492900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>432100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>495000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>440000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>339800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>88800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>433900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>249800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>228000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>28500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-849900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>246100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>276800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>309800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>270300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>331500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>234200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>232600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>263400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>254200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>265400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>288300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>265800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>282900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>261200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>364700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2663,8 +2724,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2681,11 +2742,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-173100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-103200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-119300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-160600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-108800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-123700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-61400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-22700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-39800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-22500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>121200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-21800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-45800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-107400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-37100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-68400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>604200</v>
+      </c>
+      <c r="E33" s="3">
         <v>1105800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1105300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>492900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>432100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>495000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>440000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>339800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>88800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>433900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>249800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>228000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>28500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-849900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>246100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>276800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>309800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>270300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>331500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>234200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>232600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>263400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>254200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>265400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>266300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>265800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>282900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>261200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>364700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>604200</v>
+      </c>
+      <c r="E35" s="3">
         <v>1105800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1105300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>492900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>432100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>495000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>440000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>339800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>88800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>433900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>249800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>228000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>28500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-849900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>246100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>276800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>309800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>270300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>331500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>234200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>232600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>263400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>254200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>265400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>266300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>265800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>282900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>261200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>364700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3525,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1292000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1627200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2415300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1153900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1089000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1597100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1098500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1229000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1185700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1728800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1311200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1402900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1447500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1248800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3244400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2382700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4693900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1121400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1036900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>782900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2348100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1204000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1176000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3629,135 +3719,141 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E43" s="3">
         <v>566700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>538000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>561500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>624300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>593300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>487100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>469400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>567100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>636500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>647200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>525400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>349000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>343200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>428900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>419800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>279200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>403400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>330400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>276000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>241200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>260700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>335500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>266700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>286000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>425800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>301900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>259600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>218100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>253700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>85700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>76800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>72600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>59200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>55900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>43000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>53400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>51900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>48600</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
@@ -3774,148 +3870,154 @@
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
         <v>3200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>57200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>20300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>31000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>55000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>37100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>37000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>39000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>42300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>46900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>59400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>52700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4229200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4268700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4592000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4467500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4709300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4522400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5346400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5234800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5056500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5039100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2070100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2078600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2421700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2237200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2800500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3465400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3212200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3052900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3012300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3038300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3069700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3104300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3400300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4009,293 +4111,305 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2322300</v>
+      </c>
+      <c r="E47" s="3">
         <v>3631600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3438900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3288200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2972600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3067400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3630300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3732400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3859700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2994700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1443300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1506000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1578100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1545700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1631300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1728600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1276600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1222600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1247600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1187800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1181300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1194400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1194800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>974200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>916700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>898000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>56537200</v>
+      </c>
+      <c r="E48" s="3">
         <v>57148200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>56298000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55675500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55563100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55302800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54751400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54433800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54686500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57946300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34465600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34797100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34626000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35219600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34799600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35422400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35738700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35940500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35303800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35329900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35159700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35081500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33215800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2753600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2893100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3021000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3151900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3334900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3549700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3800700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3974100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4118300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4653400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>802300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>828200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>850000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>874500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>912900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1031500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1076100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1117000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1230000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1276200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1381400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1441800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1528600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4601,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>917700</v>
+      </c>
+      <c r="E52" s="3">
         <v>770700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>813400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1177800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>996900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>662800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>267800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>347200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>439800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>611900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>537500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>368000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>399900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>378100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>390400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>513200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>626300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>610600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1113800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>846300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1002600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>533400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>827300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>656000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>747400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>735900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>652000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4797,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71105000</v>
+      </c>
+      <c r="E54" s="3">
         <v>71274600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71593700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69928400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69684400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69726900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69811200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69747600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70208200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74569800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41499300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41824100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>42065000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42048000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>44421100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>45193800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47144800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>43749200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43549000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43067900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>44717000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43208900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>42149500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,103 +4969,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1785000</v>
+      </c>
+      <c r="E57" s="3">
         <v>444000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>430000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>475300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>582000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>475200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>711100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>730700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>750800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>850200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>263600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>281300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>243700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>222200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>223100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>220100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>240400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>239100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>233400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>245800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>272000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>294300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>274900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>283900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>303900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>307400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>288100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>295500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>302400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>330400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4984,23 +5118,23 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>9000</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>8</v>
@@ -5011,8 +5145,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5029,103 +5163,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4038200</v>
+      </c>
+      <c r="E59" s="3">
         <v>4323100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4134200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3889700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3814400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3782000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3535700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3578300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3512900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4200400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2329700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2566800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2650700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2670700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2697700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2876000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3186500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3244500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3336800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3326300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3413000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3268700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3363100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5219,198 +5359,207 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45723700</v>
+      </c>
+      <c r="E61" s="3">
         <v>46483900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>47492800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46255800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46295900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46533000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47350100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47927900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48912900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50204700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>27539700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>28098600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28553100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28742100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31087100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30683900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>32760800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>29474500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29280000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29014200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30750100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29507600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>28387500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2602400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2526100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2444000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2333900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2260000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2194100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1925700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1859500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1807600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2085200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1054900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>996000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>954000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>913400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>884100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>990300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>950200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>910300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>935800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>892200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>842100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>804600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>789900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>750500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>712400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>673900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>685900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>655900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>615300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>579000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5849,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54149400</v>
+      </c>
+      <c r="E66" s="3">
         <v>54685700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55300000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53616500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53639000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53609400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54243500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54713200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>55555100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>57999000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>31644400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>32440600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32925600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>33183600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>35609700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>35559800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>37761900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>34434300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34374100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34054900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35810800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34380900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>33279700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6375,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11407200</v>
+      </c>
+      <c r="E72" s="3">
         <v>10802600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>9703300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8598000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8104800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7674900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7181000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6741800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6408100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8410300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8322600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7888700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7625700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7399700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7380700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8232500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7986100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7734600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7424100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7157200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6825300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6591700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6359700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6767,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16955600</v>
+      </c>
+      <c r="E76" s="3">
         <v>16588800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16293700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16311900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16045400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16117500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15567700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15034400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14653100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16570700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9855000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9383500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9139300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8864500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8811400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9634000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9382900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9314900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9174900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9013000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8906200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8828000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8869900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>604200</v>
+      </c>
+      <c r="E81" s="3">
         <v>1105800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1105300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>492900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>432100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>495000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>440000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>339800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>88800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>433900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>249800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>228000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>28500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-849900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>246100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>276800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>309800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>270300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>331500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>234200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>232600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>263400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>254200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>265400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>266300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>265800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>282900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>261200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>364700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,103 +7202,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>633500</v>
+      </c>
+      <c r="E83" s="3">
         <v>631400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>623000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>615600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>610500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>593700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>580900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>580700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>634400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>555800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>393400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>392200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>396600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>401800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>416000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>411800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>415800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>415900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>415300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>419100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>425800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>428500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>415300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>422100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>425500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>428200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>431000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>438900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>442800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>438200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7788,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1375700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1399600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1305200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1193200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1363400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1550600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1111900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1171900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1336600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1734500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>787800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>771200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>400400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>652500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>541000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>307900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>628900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>768300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>817100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>774500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>745700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>778400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>716700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>607300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>738000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>724300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>817200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>797200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>801500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>935200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,103 +7924,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1631500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-944700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-685000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-975800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-312900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-99100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-146100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-98600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-354100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-436100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-298900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-280300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-406700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-637200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8216,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-841800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-628600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-303100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-973200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-453600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-844200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-216100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-646600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-187300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-302600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>69300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-220800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>70000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-326200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-235200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-714600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-910900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-546100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-783200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8742,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-872700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>289000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-166500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-579700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-403700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-897800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>21683500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-660400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-550600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-288700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>270100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3189500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>321700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1197100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>965800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-93700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>212800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>928800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="K101" s="3">
-        <v>500</v>
       </c>
       <c r="L101" s="3">
         <v>500</v>
       </c>
       <c r="M101" s="3">
+        <v>500</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-340000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-781200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1289700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>53300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-493100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-145700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>56200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-568500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>380200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-58900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-82100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>180200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>882700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3582200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>103700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>226300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1159200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-449700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>428000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>205400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,442 +656,455 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1828700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1858500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1804400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1761800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1758500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1766200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1707600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1654800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1635500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1786700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1417600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1416800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1209600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1090600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1017500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1019400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1187300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1179800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1208300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1153600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1203100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1183500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1178900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>172800</v>
+      </c>
+      <c r="E9" s="3">
         <v>148600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>135200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>166000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>229200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>226000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>260900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>161400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>193200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>208100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>162000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>53500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>59000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>75300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>51200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>52200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>94700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>86900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>44100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>65200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>91700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>125900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>84800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>103300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>132500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>141200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>137800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>136300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>122400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>143300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1655900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1709900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1669200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1595800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1529300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1540200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1446700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1493400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1442300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1578600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1255600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1363300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1150600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1051400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>942200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>968200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1135100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1085100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1121400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1109500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1137900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1091800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1053000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>997300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,8 +1139,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1224,8 +1238,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,204 +1339,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E14" s="3">
         <v>-20100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-563800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-645500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-11100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>23300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2749700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>146000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>153000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>126300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>53200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>118500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1015800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>98800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>22500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>16100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>31200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>17800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>15300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>14000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>10400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>45600</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>10000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>9900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>19700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>636400</v>
+      </c>
+      <c r="E15" s="3">
         <v>633500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>631400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>623000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>615600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>610500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>593700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>580900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>580700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>634400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>555800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>393400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>392200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>396600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>401800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>416000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>411800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>415800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>415900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>415300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>419100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>425800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>425900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>412700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>417700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>422700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>425400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>428300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>435000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>438500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>433500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1577,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>969200</v>
+      </c>
+      <c r="E17" s="3">
         <v>881300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>324800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>255500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>953500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>970400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>951700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>864400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3689600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>983100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>668000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>650500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>546300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>659300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1543900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>615700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>597600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>590200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>555300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>566700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>589500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>637800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>573800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>620300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>643100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>673200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>695700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>666000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>654300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>693300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>859500</v>
+      </c>
+      <c r="E18" s="3">
         <v>977200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1479600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1506300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>805000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>795800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>756000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>790400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>734700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>434500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>748800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>559100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>544300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>358200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-524500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>571600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>582200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>618100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>598300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>636400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>594000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>541100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>572700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>523100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>486700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>541300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>514500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>528200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>535200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>616600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,498 +1816,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>111200</v>
+      </c>
+      <c r="E20" s="3">
         <v>173100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>103200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>119300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>160600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>108800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>123700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>61400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>22700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>39800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>22500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-121200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>45800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>107400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>37100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>68400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>19900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>25000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>55800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>105900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>51900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>61700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>60500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>40800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>77200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1607100</v>
+      </c>
+      <c r="E21" s="3">
         <v>1783800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2214300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2248700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1581200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1515100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1473300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1432800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1338200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1017500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1181900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>973700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>943100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>745000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-229700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1005200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1043800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1141400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1050800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1123800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1025500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>989500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>478300</v>
+      </c>
+      <c r="E22" s="3">
         <v>491500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>495900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>447000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>427400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>436200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>420300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>390800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>380800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>369500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>287200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>292900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>280800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>310500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>307300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>309700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>306100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>374900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>308900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>322600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>318300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>301800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>297000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>289400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>291000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>274900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>278200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>266000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>279200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>271300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>492400</v>
+      </c>
+      <c r="E23" s="3">
         <v>658800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1087000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1178700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>538200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>468300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>459300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>461100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>357500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>92200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>501300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>288700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>265800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>32700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-953000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>283700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>321900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>350600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>326500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>382100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>281400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>259200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>300700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>289500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>301600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>318300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>298000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>322700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>296800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>422600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E24" s="3">
         <v>94100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>110700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>75700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>65600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>64300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>50000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-278300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>62100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>40500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>39900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-106100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>38300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>43500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>42400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>49700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>36600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>28100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>39100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>42000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>38600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>60700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2420,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>416100</v>
+      </c>
+      <c r="E26" s="3">
         <v>564700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1047900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1068000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>462500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>402700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>459500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>396800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>307400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>439200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>248200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>225900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>25600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-846900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>245400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>278500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>311600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>284100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>332500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>244800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>231000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>261600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>251900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>262400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>290300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>263900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>280800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>258300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>361900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E27" s="3">
         <v>604200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1105800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1105300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>492900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>432100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>495000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>440000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>339800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>88800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>433900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>249800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>228000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>28500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-849900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>246100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>276800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>309800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>270300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>331500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>234200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>232600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>263400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>254200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>265400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>288300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>265800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>282900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>261200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>364700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2723,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2727,8 +2788,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2745,11 +2806,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2763,8 +2824,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2925,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3026,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-111200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-173100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-103200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-119300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-160600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-108800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-123700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-61400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-22700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-39800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-22500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>121200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-45800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-107400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-37100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-68400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E33" s="3">
         <v>604200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1105800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1105300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>492900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>432100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>495000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>440000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>339800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>88800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>433900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>249800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>228000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>28500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-849900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>246100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>276800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>309800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>270300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>331500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>234200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>232600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>263400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>254200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>265400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>266300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>265800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>282900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>261200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>364700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3329,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E35" s="3">
         <v>604200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1105800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1105300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>492900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>432100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>495000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>440000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>339800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>88800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>433900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>249800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>228000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>28500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-849900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>246100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>276800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>309800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>270300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>331500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>234200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>232600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>263400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>254200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>265400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>266300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>265800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>282900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>261200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>364700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3575,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3612,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1292000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1627200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2415300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1153900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1089000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1597100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1098500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1229000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1185700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1728800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1311200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1402900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1447500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1248800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3244400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2382700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4693900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1121400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1036900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>782900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2348100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1204000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,141 +3812,147 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>551300</v>
+      </c>
+      <c r="E43" s="3">
         <v>52300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>566700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>538000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>561500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>624300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>593300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>487100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>469400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>567100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>636500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>647200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>525400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>349000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>343200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>428900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>419800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>279200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>403400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>330400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>276000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>241200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>260700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>335500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>266700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>286000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>425800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>301900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>259600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>218100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>253700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>76800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>72600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>59200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>55900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>43000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>53400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>51900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>48600</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
@@ -3873,151 +3969,157 @@
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
         <v>3200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>57200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>20300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>31000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>55000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>37100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>37000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>39000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>42300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>46900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>59400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>52700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4441500</v>
+      </c>
+      <c r="E45" s="3">
         <v>4229200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4268700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4592000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4467500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4709300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4522400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5346400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5234800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5056500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5039100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2070100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2078600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2421700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2237200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2800500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3465400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3212200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3052900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3012300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3038300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3069700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3104300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4114,302 +4216,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3636900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2322300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3631600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3438900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3288200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2972600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3067400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3630300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3732400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3859700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2994700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1443300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1506000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1578100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1545700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1631300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1728600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1276600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1222600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1247600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1187800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1181300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1194400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>974200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>916700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>898000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>57581600</v>
+      </c>
+      <c r="E48" s="3">
         <v>56537200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>57148200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56298000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>55675500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>55563100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>55302800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54751400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54433800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54686500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>57946300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34465600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34797100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34626000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35219600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34799600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35422400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35738700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35940500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35303800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35329900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35159700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35081500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2561900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2753600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2893100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3021000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3151900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3334900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3549700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3800700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3974100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4118300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4653400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>802300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>828200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>850000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>874500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>912900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1031500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1076100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1117000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1230000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1276200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1381400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1441800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4620,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4721,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>554400</v>
+      </c>
+      <c r="E52" s="3">
         <v>917700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>770700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>813400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1177800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>996900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>662800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>267800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>347200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>439800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>611900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>537500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>368000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>399900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>378100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>390400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>513200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>626300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>610600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1113800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>846300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1002600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>533400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>827300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>656000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>747400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>735900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>652000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4923,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71106700</v>
+      </c>
+      <c r="E54" s="3">
         <v>71105000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71274600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71593700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>69928400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69684400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69726900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69811200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69747600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70208200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74569800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>41499300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41824100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>42065000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42048000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>44421100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>45193800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47144800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>43749200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43549000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43067900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44717000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43208900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5063,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,106 +5100,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>420600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1785000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>444000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>430000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>475300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>582000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>475200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>711100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>730700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>750800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>850200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>263600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>281300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>243700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>222200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>223100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>220100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>240400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>239100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>233400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>245800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>272000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>294300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>274900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>283900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>303900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>307400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>288100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>295500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>302400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>330400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5121,23 +5255,23 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-      <c r="T58" s="3" t="s">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9000</v>
-      </c>
-      <c r="Y58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>8</v>
@@ -5148,8 +5282,8 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5166,106 +5300,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4488600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4038200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4323100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4134200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3889700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3814400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3782000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3535700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3578300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3512900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4200400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2329700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2566800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2650700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2670700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2697700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2876000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3186500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3244500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3336800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3326300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3413000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3268700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5362,204 +5502,213 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45697200</v>
+      </c>
+      <c r="E61" s="3">
         <v>45723700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46483900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>47492800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46255800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46295900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>46533000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47350100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47927900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48912900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50204700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>27539700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>28098600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28553100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28742100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>31087100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30683900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>32760800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>29474500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29280000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29014200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30750100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29507600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2683400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2602400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2526100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2444000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2333900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2260000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2194100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1925700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1859500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1807600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2085200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1054900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>996000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>954000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>913400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>884100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>990300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>950200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>910300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>935800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>892200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>842100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>804600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>789900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>750500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>712400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>673900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>685900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>655900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>615300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>579000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5805,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5906,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6007,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54090500</v>
+      </c>
+      <c r="E66" s="3">
         <v>54149400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54685700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55300000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53616500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53639000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53609400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54243500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54713200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55555100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57999000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>31644400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>32440600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32925600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>33183600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>35609700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35559800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>37761900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>34434300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34374100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34054900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35810800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34380900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6147,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6246,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6347,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6448,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6549,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11802200</v>
+      </c>
+      <c r="E72" s="3">
         <v>11407200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10802600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9703300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8598000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8104800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7674900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7181000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6741800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6408100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8410300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8322600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7888700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7625700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7399700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7380700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8232500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7986100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7734600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7424100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7157200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6825300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6591700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6751,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6852,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6953,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17016200</v>
+      </c>
+      <c r="E76" s="3">
         <v>16955600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16588800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16293700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16311900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16045400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16117500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15567700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15034400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14653100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16570700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9855000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9383500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9139300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8864500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8811400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9634000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9382900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9314900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9174900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9013000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8906200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8828000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7155,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>448200</v>
+      </c>
+      <c r="E81" s="3">
         <v>604200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1105800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1105300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>492900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>432100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>495000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>440000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>339800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>88800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>433900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>249800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>228000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>28500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-849900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>246100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>276800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>309800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>270300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>331500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>234200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>232600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>263400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>254200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>265400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>266300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>265800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>282900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>261200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>364700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,106 +7401,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>636400</v>
+      </c>
+      <c r="E83" s="3">
         <v>633500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>631400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>623000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>615600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>610500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>593700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>580900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>580700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>634400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>555800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>393400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>392200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>396600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>401800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>416000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>411800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>415800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>415900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>415300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>419100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>425800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>428500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>415300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>422100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>425500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>428200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>431000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>438900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>442800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>438200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7601,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7702,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7803,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7904,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8005,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1408800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1375700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1399600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1305200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1193200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1363400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1550600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1111900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1171900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1336600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1734500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>787800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>771200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>400400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>652500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>541000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>307900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>628900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>768300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>817100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>774500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>745700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>778400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>716700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>607300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>738000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>724300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>817200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>797200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>801500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>935200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,106 +8145,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1623400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-944700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-685000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-975800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-312900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-19500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-99100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-146100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-98600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-61300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-354100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-436100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-298900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-280300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-406700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8345,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8446,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-850700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-841800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-628600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-303100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-973200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-453600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-844200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-216100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-646600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-187300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-302600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>69300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-220800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>70000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-326200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-235200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-714600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-910900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-546100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-783200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,8 +8586,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8451,8 +8685,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8786,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8887,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8988,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-431600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-872700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>289000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-166500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-579700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-403700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-897800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>21683500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-660400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-550600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-288700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>270100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3189500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>321700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1197100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>965800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>212800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>928800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="L101" s="3">
-        <v>500</v>
       </c>
       <c r="M101" s="3">
         <v>500</v>
       </c>
       <c r="N101" s="3">
+        <v>500</v>
+      </c>
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-700</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-400</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-340000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-781200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1289700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>53300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-493100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-145700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>56200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-568500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>380200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-58900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-82100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>180200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>882700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3582200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>103700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>226300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1159200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>428000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>205400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1828700</v>
+        <v>1948100</v>
       </c>
       <c r="E8" s="3">
-        <v>1858500</v>
+        <v>1958100</v>
       </c>
       <c r="F8" s="3">
-        <v>1804400</v>
+        <v>2018100</v>
       </c>
       <c r="G8" s="3">
-        <v>1761800</v>
+        <v>1895800</v>
       </c>
       <c r="H8" s="3">
-        <v>1758500</v>
+        <v>1891700</v>
       </c>
       <c r="I8" s="3">
-        <v>1766200</v>
+        <v>1924400</v>
       </c>
       <c r="J8" s="3">
+        <v>1865700</v>
+      </c>
+      <c r="K8" s="3">
         <v>1707600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1654800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1635500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1786700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1417600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1416800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1209600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1090600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1017500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1019400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1187300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1179800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1208300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1153600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1203100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1183500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>172800</v>
+        <v>927800</v>
       </c>
       <c r="E9" s="3">
-        <v>148600</v>
+        <v>809200</v>
       </c>
       <c r="F9" s="3">
-        <v>135200</v>
+        <v>782100</v>
       </c>
       <c r="G9" s="3">
-        <v>166000</v>
+        <v>766700</v>
       </c>
       <c r="H9" s="3">
-        <v>229200</v>
+        <v>789000</v>
       </c>
       <c r="I9" s="3">
-        <v>226000</v>
+        <v>844800</v>
       </c>
       <c r="J9" s="3">
+        <v>836500</v>
+      </c>
+      <c r="K9" s="3">
         <v>260900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>161400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>193200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>208100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>162000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>53500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>59000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>75300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>51200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>52200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>94700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>86900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>44100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>65200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>91700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>125900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>84800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>103300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>132500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>141200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>137800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>136300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>122400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>143300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1655900</v>
+        <v>1020300</v>
       </c>
       <c r="E10" s="3">
-        <v>1709900</v>
+        <v>1148900</v>
       </c>
       <c r="F10" s="3">
-        <v>1669200</v>
+        <v>1236000</v>
       </c>
       <c r="G10" s="3">
-        <v>1595800</v>
+        <v>1129200</v>
       </c>
       <c r="H10" s="3">
-        <v>1529300</v>
+        <v>1102700</v>
       </c>
       <c r="I10" s="3">
-        <v>1540200</v>
+        <v>1079500</v>
       </c>
       <c r="J10" s="3">
+        <v>1029200</v>
+      </c>
+      <c r="K10" s="3">
         <v>1446700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1493400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1442300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1578600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1255600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1363300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1150600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1051400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>942200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>968200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1135100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1085100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1121400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1109500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1137900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1091800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>997300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1153,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,210 +1359,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>34700</v>
+        <v>-9300</v>
       </c>
       <c r="E14" s="3">
-        <v>-20100</v>
+        <v>52900</v>
       </c>
       <c r="F14" s="3">
-        <v>-563800</v>
+        <v>-33600</v>
       </c>
       <c r="G14" s="3">
-        <v>-645500</v>
+        <v>-575500</v>
       </c>
       <c r="H14" s="3">
-        <v>-11100</v>
+        <v>-634900</v>
       </c>
       <c r="I14" s="3">
-        <v>23300</v>
+        <v>-5800</v>
       </c>
       <c r="J14" s="3">
+        <v>14000</v>
+      </c>
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>16700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>21900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2749700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>146000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>153000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>126300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>53200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>118500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1015800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>98800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>22500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>16100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>31200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>17800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>10400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>45600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>10000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>9900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>19700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>636400</v>
+        <v>7900</v>
       </c>
       <c r="E15" s="3">
-        <v>633500</v>
+        <v>8100</v>
       </c>
       <c r="F15" s="3">
-        <v>631400</v>
+        <v>7900</v>
       </c>
       <c r="G15" s="3">
-        <v>623000</v>
+        <v>17900</v>
       </c>
       <c r="H15" s="3">
-        <v>615600</v>
+        <v>9200</v>
       </c>
       <c r="I15" s="3">
-        <v>610500</v>
+        <v>8300</v>
       </c>
       <c r="J15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K15" s="3">
         <v>593700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>580900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>580700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>634400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>555800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>393400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>392200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>396600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>401800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>416000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>411800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>415800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>415900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>415300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>419100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>425800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>425900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>412700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>417700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>422700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>425400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>428300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>435000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>438500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>433500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>969200</v>
+        <v>1049100</v>
       </c>
       <c r="E17" s="3">
-        <v>881300</v>
+        <v>934500</v>
       </c>
       <c r="F17" s="3">
-        <v>324800</v>
+        <v>901400</v>
       </c>
       <c r="G17" s="3">
-        <v>255500</v>
+        <v>888500</v>
       </c>
       <c r="H17" s="3">
-        <v>953500</v>
+        <v>900900</v>
       </c>
       <c r="I17" s="3">
-        <v>970400</v>
+        <v>964600</v>
       </c>
       <c r="J17" s="3">
+        <v>947100</v>
+      </c>
+      <c r="K17" s="3">
         <v>951700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>864400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3689600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>983100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>668000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>650500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>546300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>659300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1543900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>615700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>597600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>590200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>555300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>566700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>589500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>637800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>573800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>620300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>643100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>673200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>695700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>666000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>654300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>693300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>859500</v>
+        <v>899000</v>
       </c>
       <c r="E18" s="3">
-        <v>977200</v>
+        <v>1023600</v>
       </c>
       <c r="F18" s="3">
-        <v>1479600</v>
+        <v>1116700</v>
       </c>
       <c r="G18" s="3">
-        <v>1506300</v>
+        <v>1007300</v>
       </c>
       <c r="H18" s="3">
-        <v>805000</v>
+        <v>990800</v>
       </c>
       <c r="I18" s="3">
-        <v>795800</v>
+        <v>959800</v>
       </c>
       <c r="J18" s="3">
+        <v>918600</v>
+      </c>
+      <c r="K18" s="3">
         <v>756000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>790400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>734700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>434500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>748800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>559100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>544300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>358200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-524500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>571600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>582200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>618100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>598300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>636400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>594000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>541100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>572700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>523100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>486700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>541300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>514500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>528200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>535200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>616600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,513 +1850,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>111200</v>
+        <v>-43800</v>
       </c>
       <c r="E20" s="3">
-        <v>173100</v>
+        <v>-32100</v>
       </c>
       <c r="F20" s="3">
-        <v>103200</v>
+        <v>-39500</v>
       </c>
       <c r="G20" s="3">
-        <v>119300</v>
+        <v>-58800</v>
       </c>
       <c r="H20" s="3">
-        <v>160600</v>
+        <v>-41000</v>
       </c>
       <c r="I20" s="3">
-        <v>108800</v>
+        <v>-34400</v>
       </c>
       <c r="J20" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="K20" s="3">
         <v>123700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>61400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>22700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>39800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>22500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-15000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-121200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>21800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>45800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>107400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>37100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>68400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>19900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>55800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>105900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>51900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>61700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>60500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>40800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>77200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1607100</v>
+        <v>950600</v>
       </c>
       <c r="E21" s="3">
-        <v>1783800</v>
+        <v>1063800</v>
       </c>
       <c r="F21" s="3">
-        <v>2214300</v>
+        <v>1164200</v>
       </c>
       <c r="G21" s="3">
-        <v>2248700</v>
+        <v>1084000</v>
       </c>
       <c r="H21" s="3">
-        <v>1581200</v>
+        <v>1041000</v>
       </c>
       <c r="I21" s="3">
-        <v>1515100</v>
+        <v>1002400</v>
       </c>
       <c r="J21" s="3">
+        <v>959400</v>
+      </c>
+      <c r="K21" s="3">
         <v>1473300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1432800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1338200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1017500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1181900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>973700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>943100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>745000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-229700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1005200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1043800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1141400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1050800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1123800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1025500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>989500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>516300</v>
+      </c>
+      <c r="E22" s="3">
         <v>478300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>491500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>495900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>447000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>427400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>436200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>420300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>390800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>380800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>369500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>287200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>292900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>280800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>310500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>307300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>309700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>306100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>374900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>308900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>322600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>318300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>301800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>297000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>289400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>291000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>274900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>278200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>266000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>279200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>271300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>492400</v>
+        <v>435800</v>
       </c>
       <c r="E23" s="3">
-        <v>658800</v>
+        <v>524500</v>
       </c>
       <c r="F23" s="3">
-        <v>1087000</v>
+        <v>698300</v>
       </c>
       <c r="G23" s="3">
-        <v>1178700</v>
+        <v>1145700</v>
       </c>
       <c r="H23" s="3">
-        <v>538200</v>
+        <v>1219700</v>
       </c>
       <c r="I23" s="3">
-        <v>468300</v>
+        <v>572600</v>
       </c>
       <c r="J23" s="3">
+        <v>500900</v>
+      </c>
+      <c r="K23" s="3">
         <v>459300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>461100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>357500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>92200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>501300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>288700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>265800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>32700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-953000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>283700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>321900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>350600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>326500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>382100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>281400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>259200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>300700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>289500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>301600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>318300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>298000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>322700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>296800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>422600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E24" s="3">
         <v>76300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>94100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>110700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>75700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>65600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>64300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>50000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-278300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>20000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>62100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>40500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-106100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>38300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>39000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>42400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>49700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>28100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>39200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>34200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>42000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>38600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>60700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>416100</v>
+        <v>375000</v>
       </c>
       <c r="E26" s="3">
-        <v>564700</v>
+        <v>448200</v>
       </c>
       <c r="F26" s="3">
-        <v>1047900</v>
+        <v>604200</v>
       </c>
       <c r="G26" s="3">
-        <v>1068000</v>
+        <v>1106700</v>
       </c>
       <c r="H26" s="3">
-        <v>462500</v>
+        <v>1109000</v>
       </c>
       <c r="I26" s="3">
-        <v>402700</v>
+        <v>496900</v>
       </c>
       <c r="J26" s="3">
+        <v>435300</v>
+      </c>
+      <c r="K26" s="3">
         <v>459500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>396800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>307400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>72100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>439200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>248200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>225900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>25600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-846900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>245400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>278500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>311600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>284100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>332500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>244800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>231000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>261600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>251900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>262400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>290300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>263900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>280800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>258300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>361900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E27" s="3">
         <v>448200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>604200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1105800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1105300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>492900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>432100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>495000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>440000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>339800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>88800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>433900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>249800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>228000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>28500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-849900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>246100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>276800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>309800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>270300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>331500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>234200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>232600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>263400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>254200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>265400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>288300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>265800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>282900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>261200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>364700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2791,8 +2852,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2809,11 +2870,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2827,8 +2888,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,210 +3096,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-111200</v>
+        <v>43800</v>
       </c>
       <c r="E32" s="3">
-        <v>-173100</v>
+        <v>32100</v>
       </c>
       <c r="F32" s="3">
-        <v>-103200</v>
+        <v>39500</v>
       </c>
       <c r="G32" s="3">
-        <v>-119300</v>
+        <v>58800</v>
       </c>
       <c r="H32" s="3">
-        <v>-160600</v>
+        <v>41000</v>
       </c>
       <c r="I32" s="3">
-        <v>-108800</v>
+        <v>34400</v>
       </c>
       <c r="J32" s="3">
+        <v>32500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-123700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-61400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-22700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-39800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>15000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>121200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-21800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-45800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-107400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-37100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-68400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E33" s="3">
         <v>448200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>604200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1105800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1105300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>492900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>432100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>495000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>440000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>339800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>88800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>433900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>249800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>228000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>28500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-849900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>246100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>276800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>309800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>270300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>331500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>234200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>232600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>263400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>254200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>265400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>266300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>265800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>282900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>261200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>364700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E35" s="3">
         <v>448200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>604200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1105800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1105300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>492900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>432100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>495000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>440000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>339800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>88800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>433900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>249800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>228000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>28500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-849900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>246100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>276800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>309800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>270300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>331500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>234200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>232600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>263400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>254200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>265400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>266300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>265800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>282900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>261200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>364700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,132 +3699,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3754500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1436000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1292000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1627200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2415300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1153900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1089000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1597100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1098500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1229000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1185700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1728800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1311200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1402900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1447500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1248800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3244400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2382700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4693900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1121400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1036900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>782900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2348100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>143500</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>153200</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>130600</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>244500</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>220600</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>175700</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3815,147 +3905,153 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>551300</v>
+        <v>3484300</v>
       </c>
       <c r="E43" s="3">
-        <v>52300</v>
+        <v>3211000</v>
       </c>
       <c r="F43" s="3">
-        <v>566700</v>
+        <v>3829100</v>
       </c>
       <c r="G43" s="3">
-        <v>538000</v>
+        <v>3832200</v>
       </c>
       <c r="H43" s="3">
-        <v>561500</v>
+        <v>3674200</v>
       </c>
       <c r="I43" s="3">
-        <v>624300</v>
+        <v>3650900</v>
       </c>
       <c r="J43" s="3">
+        <v>3445600</v>
+      </c>
+      <c r="K43" s="3">
         <v>593300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>487100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>469400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>567100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>636500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>647200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>525400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>349000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>343200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>428900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>419800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>279200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>403400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>330400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>276000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>241200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>260700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>335500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>266700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>286000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>425800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>301900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>259600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>218100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>253700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E44" s="3">
         <v>62500</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F44" s="3">
+        <v>72900</v>
+      </c>
+      <c r="G44" s="3">
         <v>85700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>76800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>72600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>59200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>55900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>43000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>53400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>51900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>48600</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
@@ -3972,177 +4068,183 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
         <v>3200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>57200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>20300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>31000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>55000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>37100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>37000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>39000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>42300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>46900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>59400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>52700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4441500</v>
+        <v>520900</v>
       </c>
       <c r="E45" s="3">
-        <v>4229200</v>
+        <v>104900</v>
       </c>
       <c r="F45" s="3">
-        <v>4268700</v>
+        <v>459100</v>
       </c>
       <c r="G45" s="3">
-        <v>4592000</v>
+        <v>296700</v>
       </c>
       <c r="H45" s="3">
-        <v>4467500</v>
+        <v>420600</v>
       </c>
       <c r="I45" s="3">
-        <v>4709300</v>
+        <v>808500</v>
       </c>
       <c r="J45" s="3">
+        <v>607500</v>
+      </c>
+      <c r="K45" s="3">
         <v>4522400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5346400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5234800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5056500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5039100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2070100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2078600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2421700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2237200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2800500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3465400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3212200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3052900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3012300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3038300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3069700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>8095200</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>5134100</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>5999900</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>6170700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>7022800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>6069600</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>5551600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4219,311 +4321,323 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3636900</v>
+        <v>1162800</v>
       </c>
       <c r="E47" s="3">
-        <v>2322300</v>
+        <v>1117700</v>
       </c>
       <c r="F47" s="3">
-        <v>3631600</v>
+        <v>1107300</v>
       </c>
       <c r="G47" s="3">
-        <v>3438900</v>
+        <v>1058600</v>
       </c>
       <c r="H47" s="3">
-        <v>3288200</v>
+        <v>1011200</v>
       </c>
       <c r="I47" s="3">
-        <v>2972600</v>
+        <v>968500</v>
       </c>
       <c r="J47" s="3">
+        <v>914200</v>
+      </c>
+      <c r="K47" s="3">
         <v>3067400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3630300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3732400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3859700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2994700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1443300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1506000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1578100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1545700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1631300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1728600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1276600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1222600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1247600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1187800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1181300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>974200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>916700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>898000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>57581600</v>
+        <v>61000</v>
       </c>
       <c r="E48" s="3">
-        <v>56537200</v>
+        <v>66500</v>
       </c>
       <c r="F48" s="3">
-        <v>57148200</v>
+        <v>72000</v>
       </c>
       <c r="G48" s="3">
-        <v>56298000</v>
+        <v>57000</v>
       </c>
       <c r="H48" s="3">
-        <v>55675500</v>
+        <v>60700</v>
       </c>
       <c r="I48" s="3">
-        <v>55563100</v>
+        <v>70600</v>
       </c>
       <c r="J48" s="3">
+        <v>75800</v>
+      </c>
+      <c r="K48" s="3">
         <v>55302800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>54751400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54433800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54686500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>57946300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34465600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34797100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34626000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35219600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34799600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35422400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35738700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35940500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35303800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35329900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35159700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2561900</v>
+        <v>2566600</v>
       </c>
       <c r="E49" s="3">
-        <v>2753600</v>
+        <v>2698900</v>
       </c>
       <c r="F49" s="3">
-        <v>2893100</v>
+        <v>2894400</v>
       </c>
       <c r="G49" s="3">
-        <v>3021000</v>
+        <v>3045200</v>
       </c>
       <c r="H49" s="3">
-        <v>3151900</v>
+        <v>3176900</v>
       </c>
       <c r="I49" s="3">
-        <v>3334900</v>
+        <v>3310800</v>
       </c>
       <c r="J49" s="3">
+        <v>3494300</v>
+      </c>
+      <c r="K49" s="3">
         <v>3549700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3800700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3974100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4118300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4653400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>802300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>828200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>850000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>874500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>912900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1031500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1076100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1117000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1230000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1276200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1381400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,109 +4841,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>554400</v>
+        <v>61659400</v>
       </c>
       <c r="E52" s="3">
-        <v>917700</v>
+        <v>61816200</v>
       </c>
       <c r="F52" s="3">
-        <v>770700</v>
+        <v>60766400</v>
       </c>
       <c r="G52" s="3">
-        <v>813400</v>
+        <v>60667400</v>
       </c>
       <c r="H52" s="3">
-        <v>1177800</v>
+        <v>60120700</v>
       </c>
       <c r="I52" s="3">
-        <v>996900</v>
+        <v>59302700</v>
       </c>
       <c r="J52" s="3">
+        <v>59433700</v>
+      </c>
+      <c r="K52" s="3">
         <v>662800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>267800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>347200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>439800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>611900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>537500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>368000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>399900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>378100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>390400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>513200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>626300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>610600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1113800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>846300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1002600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>533400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>827300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>656000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>747400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>735900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>652000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73824900</v>
+      </c>
+      <c r="E54" s="3">
         <v>71106700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71105000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71274600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71593700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>69928400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69684400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69726900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69811200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69747600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70208200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74569800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41499300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41824100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42065000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42048000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>44421100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>45193800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47144800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>43749200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43549000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43067900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44717000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,132 +5231,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>423300</v>
+      </c>
+      <c r="E57" s="3">
         <v>420600</v>
       </c>
-      <c r="E57" s="3">
-        <v>1785000</v>
-      </c>
       <c r="F57" s="3">
+        <v>429400</v>
+      </c>
+      <c r="G57" s="3">
         <v>444000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>430000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>475300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>582000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>475200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>711100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>730700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>750800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>850200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>263600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>281300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>243700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>222200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>223100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>220100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>240400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>239100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>233400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>245800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>272000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>294300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>274900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>283900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>303900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>307400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>288100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>295500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>302400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>330400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>80500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>54200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>64000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>143900</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>44500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>62500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5258,23 +5392,23 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-      <c r="U58" s="3" t="s">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>11700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>9000</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>8</v>
@@ -5285,8 +5419,8 @@
       <c r="AC58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
+      <c r="AD58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5303,132 +5437,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>4488600</v>
-      </c>
-      <c r="E59" s="3">
-        <v>4038200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>4323100</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4134200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3889700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3814400</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>3782000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3535700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3578300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3512900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4200400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2329700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2566800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2650700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2670700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2697700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2876000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3186500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3244500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3336800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3326300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3413000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>4084000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>3848600</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>3889600</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>3800200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>3530100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>3400800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>3480500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5505,210 +5645,219 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>45697200</v>
+        <v>48418000</v>
       </c>
       <c r="E61" s="3">
-        <v>45723700</v>
+        <v>45759800</v>
       </c>
       <c r="F61" s="3">
-        <v>46483900</v>
+        <v>45785300</v>
       </c>
       <c r="G61" s="3">
-        <v>47492800</v>
+        <v>46513000</v>
       </c>
       <c r="H61" s="3">
-        <v>46255800</v>
+        <v>47581200</v>
       </c>
       <c r="I61" s="3">
-        <v>46295900</v>
+        <v>46343800</v>
       </c>
       <c r="J61" s="3">
+        <v>46381700</v>
+      </c>
+      <c r="K61" s="3">
         <v>46533000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>47350100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47927900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48912900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50204700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>27539700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>28098600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28553100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28742100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>31087100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30683900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>32760800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>29474500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29280000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29014200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>30750100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2683400</v>
+        <v>1050400</v>
       </c>
       <c r="E62" s="3">
-        <v>2602400</v>
+        <v>1007900</v>
       </c>
       <c r="F62" s="3">
-        <v>2526100</v>
+        <v>1063100</v>
       </c>
       <c r="G62" s="3">
-        <v>2444000</v>
+        <v>1018700</v>
       </c>
       <c r="H62" s="3">
-        <v>2333900</v>
+        <v>945900</v>
       </c>
       <c r="I62" s="3">
-        <v>2260000</v>
+        <v>876600</v>
       </c>
       <c r="J62" s="3">
+        <v>845000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2194100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1925700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1859500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1807600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2085200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1054900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>996000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>954000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>913400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>884100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>990300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>950200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>910300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>935800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>892200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>842100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>804600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>789900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>750500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>712400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>673900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>685900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>655900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>615300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>579000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>54090500</v>
+        <v>57072400</v>
       </c>
       <c r="E66" s="3">
-        <v>54149400</v>
+        <v>54090200</v>
       </c>
       <c r="F66" s="3">
-        <v>54685700</v>
+        <v>54149200</v>
       </c>
       <c r="G66" s="3">
-        <v>55300000</v>
+        <v>54685500</v>
       </c>
       <c r="H66" s="3">
-        <v>53616500</v>
+        <v>55221500</v>
       </c>
       <c r="I66" s="3">
-        <v>53639000</v>
+        <v>53537900</v>
       </c>
       <c r="J66" s="3">
+        <v>53560800</v>
+      </c>
+      <c r="K66" s="3">
         <v>53609400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54243500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54713200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55555100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>57999000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31644400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>32440600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32925600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>33183600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>35609700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35559800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>37761900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>34434300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34374100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34054900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35810800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12129400</v>
+      </c>
+      <c r="E72" s="3">
         <v>11802200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11407200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10802600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9703300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8598000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8104800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7674900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7181000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6741800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6408100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8410300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8322600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7888700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7625700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7399700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7380700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8232500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7986100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7734600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7424100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7157200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6825300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16752300</v>
+      </c>
+      <c r="E76" s="3">
         <v>17016200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16955600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16588800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16293700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16311900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16045400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16117500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>15567700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15034400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14653100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16570700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9855000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9383500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9139300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8864500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8811400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9634000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9382900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9314900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9174900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9013000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8906200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E81" s="3">
         <v>448200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>604200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1105800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1105300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>492900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>432100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>495000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>440000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>339800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>88800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>433900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>249800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>228000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>28500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-849900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>246100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>276800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>309800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>270300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>331500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>234200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>232600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>263400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>254200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>265400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>266300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>265800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>282900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>261200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>364700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,109 +7600,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>636400</v>
+        <v>4200</v>
       </c>
       <c r="E83" s="3">
-        <v>633500</v>
+        <v>2300</v>
       </c>
       <c r="F83" s="3">
-        <v>631400</v>
+        <v>3200</v>
       </c>
       <c r="G83" s="3">
-        <v>623000</v>
+        <v>8900</v>
       </c>
       <c r="H83" s="3">
-        <v>615600</v>
+        <v>-1800</v>
       </c>
       <c r="I83" s="3">
-        <v>610500</v>
+        <v>3300</v>
       </c>
       <c r="J83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K83" s="3">
         <v>593700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>580900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>580700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>634400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>555800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>393400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>392200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>396600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>401800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>416000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>411800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>415800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>415900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>415300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>419100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>425800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>428500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>415300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>422100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>425500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>428200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>431000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>438900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>442800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>438200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1367800</v>
+      </c>
+      <c r="E89" s="3">
         <v>1408800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1375700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1399600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1305200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1193200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1363400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1550600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1111900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1171900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1336600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1734500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>787800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>771200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>400400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>652500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>541000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>307900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>628900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>768300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>817100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>774500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>745700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>778400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>716700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>607300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>738000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>724300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>817200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>797200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>801500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>935200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,109 +8366,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1733700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-944700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-685000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-975800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-312900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-99100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-146100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-98600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-61300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-354100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-436100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-298900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-280300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,109 +8676,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1372600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-850700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-841800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-628600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-303100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-973200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-453600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-844200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-216100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-646600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-187300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-302600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>69300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-220800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>70000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-326200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-235200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-714600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-910900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-546100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-783200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,31 +8820,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>48000</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+        <v>41800</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,307 +9234,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2344500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-431600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-872700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>289000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-166500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-579700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-600300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-403700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-897800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>21683500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-660400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-550600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-288700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>270100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3189500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>321700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1197100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>965800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>212800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>928800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>-1500</v>
       </c>
       <c r="E101" s="3">
-        <v>-1200</v>
+        <v>-200</v>
       </c>
       <c r="F101" s="3">
-        <v>2400</v>
+        <v>1300</v>
       </c>
       <c r="G101" s="3">
-        <v>-1500</v>
+        <v>3400</v>
       </c>
       <c r="H101" s="3">
-        <v>-200</v>
+        <v>-9800</v>
       </c>
       <c r="I101" s="3">
-        <v>1300</v>
+        <v>-1800</v>
       </c>
       <c r="J101" s="3">
+        <v>500</v>
+      </c>
+      <c r="K101" s="3">
         <v>3400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="M101" s="3">
-        <v>500</v>
       </c>
       <c r="N101" s="3">
         <v>500</v>
       </c>
       <c r="O101" s="3">
+        <v>500</v>
+      </c>
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1500</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-700</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2342300</v>
+      </c>
+      <c r="E102" s="3">
         <v>126700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-340000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-781200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1289700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>53300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-493100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-145700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>56200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-568500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>380200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-58900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-82100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>180200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>882700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3582200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>103700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>226300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1159200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>428000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>205400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,468 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2072300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1948100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1958100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2018100</v>
       </c>
-      <c r="G8" s="3">
-        <v>1895800</v>
-      </c>
       <c r="H8" s="3">
+        <v>1898600</v>
+      </c>
+      <c r="I8" s="3">
         <v>1891700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1924400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1865700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1707600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1654800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1635500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1786700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1417600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1416800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1209600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1090600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1017500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1019400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1187300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1179800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1208300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1153600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1203100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1183500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>871300</v>
+      </c>
+      <c r="E9" s="3">
         <v>927800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>809200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>782100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>766700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>789000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>844800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>836500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>260900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>161400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>193200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>208100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>162000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>53500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>59000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>39200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>75300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>51200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>52200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>94700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>86900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>44100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>65200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>91700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>125900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>84800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>103300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>132500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>141200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>137800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>136300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>122400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>143300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1201000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1020300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1148900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1236000</v>
       </c>
-      <c r="G10" s="3">
-        <v>1129200</v>
-      </c>
       <c r="H10" s="3">
+        <v>1132000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1102700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1079500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1029200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1446700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1493400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1442300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1578600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1255600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1363300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1150600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1051400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>942200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>968200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1135100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1085100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1121400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1109500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1137900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1091800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>997300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,216 +1378,225 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-146800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-9300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>52900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-33600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-575500</v>
-      </c>
       <c r="H14" s="3">
+        <v>-572700</v>
+      </c>
+      <c r="I14" s="3">
         <v>-634900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-5800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>16700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2749700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>146000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>153000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>126300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>53200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>118500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1015800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>98800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>22500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>16100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>31200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>17800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>12800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>2100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>10400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>45600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>10000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>9900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>19700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7900</v>
       </c>
-      <c r="G15" s="3">
-        <v>17900</v>
-      </c>
       <c r="H15" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I15" s="3">
         <v>9200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>593700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>580900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>580700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>634400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>555800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>393400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>392200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>396600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>401800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>416000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>411800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>415800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>415900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>415300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>419100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>425800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>425900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>412700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>417700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>422700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>425400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>428300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>435000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>438500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>433500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>994300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1049100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>934500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>901400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>888500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>964600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>947100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>951700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>864400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3689600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>983100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>668000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>650500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>546300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>659300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1543900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>615700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>597600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>590200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>555300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>566700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>589500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>637800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>573800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>620300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>643100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>673200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>695700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>666000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>654300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>693300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1078000</v>
+      </c>
+      <c r="E18" s="3">
         <v>899000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1023600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1116700</v>
       </c>
-      <c r="G18" s="3">
-        <v>1007300</v>
-      </c>
       <c r="H18" s="3">
+        <v>1010100</v>
+      </c>
+      <c r="I18" s="3">
         <v>990800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>959800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>918600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>756000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>790400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>734700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>434500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>748800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>559100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>544300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>358200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-524500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>571600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>582200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>618100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>598300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>636400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>594000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>541100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>572700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>523100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>486700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>541300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>514500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>528200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>535200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>616600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,528 +1883,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-43800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-32100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-39500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-58800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-41000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-34400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-32500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>123700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>61400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>39800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-121200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>21800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>45800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>107400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>37100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>68400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>19900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>55800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>105900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>51900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>61700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>60500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>40800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>77200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1129600</v>
+      </c>
+      <c r="E21" s="3">
         <v>950600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1063800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1164200</v>
       </c>
-      <c r="G21" s="3">
-        <v>1084000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1077000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1041000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1002400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>959400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1473300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1432800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1338200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1017500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1181900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>973700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>943100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>745000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-229700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1005200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1043800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1141400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1050800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1123800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1025500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>989500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>504700</v>
+      </c>
+      <c r="E22" s="3">
         <v>516300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>478300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>491500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>495900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>447000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>427400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>436200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>420300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>390800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>380800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>369500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>287200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>292900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>280800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>310500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>307300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>309700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>306100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>374900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>308900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>322600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>318300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>301800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>297000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>289400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>291000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>274900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>278200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>266000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>279200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>271300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>763700</v>
+      </c>
+      <c r="E23" s="3">
         <v>435800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>524500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>698300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1145700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1219700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>572600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>500900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>459300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>461100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>357500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>92200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>501300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>288700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>265800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>32700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-953000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>283700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>321900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>350600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>326500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>382100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>281400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>259200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>300700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>289500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>301600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>318300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>298000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>322700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>296800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>422600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E24" s="3">
         <v>60700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>76300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>94100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>39000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>110700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>75700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>65600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>50000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-278300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>20000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>62100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>40500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>39900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-106100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>38300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>49700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>37600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>39200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>34200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>42000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>38600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>60700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>671200</v>
+      </c>
+      <c r="E26" s="3">
         <v>375000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>448200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>604200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1106700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1109000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>496900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>435300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>459500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>396800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>307400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>439200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>248200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>225900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>25600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-846900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>245400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>278500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>311600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>284100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>332500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>244800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>231000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>261600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>251900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>262400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>290300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>263900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>280800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>258300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>361900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>671200</v>
+      </c>
+      <c r="E27" s="3">
         <v>375000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>448200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>604200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1105800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1105300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>492900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>432100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>495000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>440000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>339800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>88800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>433900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>249800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>228000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>28500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-849900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>246100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>276800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>309800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>270300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>331500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>234200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>232600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>263400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>254200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>265400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>288300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>265800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>282900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>261200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>364700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2855,8 +2915,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2873,11 +2933,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2891,8 +2951,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,216 +3165,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E32" s="3">
         <v>43800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>32100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>39500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>58800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>41000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>34400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>32500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-123700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-61400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>121200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-21800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-45800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-107400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-68400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>671200</v>
+      </c>
+      <c r="E33" s="3">
         <v>375000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>448200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>604200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1105800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1105300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>492900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>432100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>495000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>440000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>339800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>88800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>433900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>249800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>228000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>28500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-849900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>246100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>276800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>309800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>270300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>331500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>234200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>232600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>263400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>254200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>265400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>266300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>265800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>282900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>261200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>364700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>671200</v>
+      </c>
+      <c r="E35" s="3">
         <v>375000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>448200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>604200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1105800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1105300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>492900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>432100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>495000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>440000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>339800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>88800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>433900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>249800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>228000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>28500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-849900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>246100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>276800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>309800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>270300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>331500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>234200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>232600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>263400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>254200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>265400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>266300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>265800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>282900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>261200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>364700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,139 +3785,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1209200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3754500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1436000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1292000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1627200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2415300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1153900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1089000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1597100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1098500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1229000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1185700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1728800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1311200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1402900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1447500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1248800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3244400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2382700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4693900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1121400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1036900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>782900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2348100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>81800</v>
+      </c>
+      <c r="E42" s="3">
         <v>55700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>143500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>153200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>130600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>244500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>220600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>175700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3908,153 +3997,159 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3449600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3484300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3211000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3829100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3832200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3674200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3650900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3445600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>593300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>487100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>469400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>567100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>636500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>647200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>525400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>349000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>343200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>428900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>419800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>279200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>403400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>330400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>276000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>241200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>260700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>335500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>266700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>286000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>425800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>301900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>259600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>218100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>253700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E44" s="3">
         <v>80000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>62500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>72900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>85700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>76800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>72600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>59200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>55900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>43000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>53400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>51900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>48600</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
@@ -4071,184 +4166,190 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
         <v>3200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>6400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>57200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>20300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>31000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>55000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>37100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>37000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>39000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>42300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>46900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>59400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>466200</v>
+      </c>
+      <c r="E45" s="3">
         <v>520900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>104900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>459100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>296700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>420600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>808500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>607500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4522400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5346400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5234800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5056500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5039100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2070100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2078600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2421700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2237200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3465400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3212200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3052900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3012300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3038300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3069700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5490100</v>
+      </c>
+      <c r="E46" s="3">
         <v>8095200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5134100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5999900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6170700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7022800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6069600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5551600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4324,320 +4425,332 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1205700</v>
+      </c>
+      <c r="E47" s="3">
         <v>1162800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1117700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1107300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1058600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1011200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>968500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>914200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3067400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3630300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3732400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3859700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2994700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1443300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1506000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1578100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1545700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1631300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1728600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1276600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1222600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1247600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1187800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1181300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>974200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>916700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>898000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E48" s="3">
         <v>61000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>72000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>57000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>60700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>70600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>75800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>55302800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>54751400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54433800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>54686500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>57946300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34465600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34797100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34626000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>35219600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34799600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35422400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35738700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35940500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35303800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35329900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35159700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2403300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2566600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2698900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2894400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3045200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3176900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3310800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3494300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3549700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3800700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3974100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4118300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4653400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>802300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>828200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>850000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>874500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>912900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1031500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1076100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1117000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1230000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1276200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1381400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,112 +4960,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62036000</v>
+      </c>
+      <c r="E52" s="3">
         <v>61659400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61816200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>60766400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60667400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60120700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59302700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59433700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>662800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>267800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>347200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>439800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>611900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>537500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>368000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>399900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>378100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>390400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>513200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>626300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>610600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1113800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>846300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1002600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>533400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>827300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>656000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>747400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>735900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>652000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71442000</v>
+      </c>
+      <c r="E54" s="3">
         <v>73824900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71106700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71105000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71274600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71593700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69928400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69684400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69726900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69811200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69747600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70208200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>74569800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41499300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41824100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42065000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42048000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>44421100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>45193800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47144800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43749200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43549000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43067900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>44717000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,139 +5361,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>465700</v>
+      </c>
+      <c r="E57" s="3">
         <v>423300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>420600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>429400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>444000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>430000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>475300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>582000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>475200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>711100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>730700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>750800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>850200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>263600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>281300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>243700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>222200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>223100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>220100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>240400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>239100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>233400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>245800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>272000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>294300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>274900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>283900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>303900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>307400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>288100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>295500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>302400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>330400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E58" s="3">
         <v>80500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>54200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64000</v>
       </c>
-      <c r="G58" s="3">
-        <v>143900</v>
-      </c>
       <c r="H58" s="3">
+        <v>80800</v>
+      </c>
+      <c r="I58" s="3">
         <v>3500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>62500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5395,23 +5528,23 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-      <c r="V58" s="3" t="s">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB58" s="3" t="s">
         <v>8</v>
@@ -5422,8 +5555,8 @@
       <c r="AD58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -5440,8 +5573,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5466,113 +5602,116 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>3782000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3535700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3578300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3512900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4200400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2329700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2566800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2650700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2670700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2697700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2876000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3186500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3244500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3336800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3326300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3413000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4245100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4084000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3848600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3889600</v>
       </c>
-      <c r="G60" s="3">
-        <v>3800200</v>
-      </c>
       <c r="H60" s="3">
+        <v>3737200</v>
+      </c>
+      <c r="I60" s="3">
         <v>3530100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3400800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3480500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5648,216 +5787,225 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>45321800</v>
+      </c>
+      <c r="E61" s="3">
         <v>48418000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45759800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45785300</v>
       </c>
-      <c r="G61" s="3">
-        <v>46513000</v>
-      </c>
       <c r="H61" s="3">
+        <v>46576000</v>
+      </c>
+      <c r="I61" s="3">
         <v>47581200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>46343800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46381700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46533000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47350100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47927900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>48912900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50204700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>27539700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>28098600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28553100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28742100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>31087100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30683900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>32760800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>29474500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29280000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29014200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>30750100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1092600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1050400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1007900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1063100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1018700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>945900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>876600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>845000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2194100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1925700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1859500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1807600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2085200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1054900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>996000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>954000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>913400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>884100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>990300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>950200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>910300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>935800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>892200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>842100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>804600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>789900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>750500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>712400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>673900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>685900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>655900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>615300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>579000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>54257100</v>
+      </c>
+      <c r="E66" s="3">
         <v>57072400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54090200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54149200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54685500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>55221500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>53537900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53560800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53609400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54243500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54713200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>55555100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>57999000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31644400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>32440600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32925600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>33183600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>35609700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35559800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>37761900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>34434300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34374100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34054900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>35810800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6896,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12755800</v>
+      </c>
+      <c r="E72" s="3">
         <v>12129400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>11802200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11407200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10802600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9703300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8598000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8104800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7674900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7181000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6741800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6408100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8410300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8322600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7888700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7625700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7399700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7380700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8232500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7986100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7734600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7424100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7157200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6825300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7324,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17184600</v>
+      </c>
+      <c r="E76" s="3">
         <v>16752300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17016200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16955600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16588800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16293700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16311900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16045400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16117500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15567700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15034400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14653100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16570700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9855000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9383500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9139300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8864500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8811400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9634000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9382900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9314900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9174900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9013000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8906200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>671200</v>
+      </c>
+      <c r="E81" s="3">
         <v>375000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>448200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>604200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1105800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1105300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>492900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>432100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>495000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>440000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>339800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>88800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>433900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>249800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>228000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>28500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-849900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>246100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>276800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>309800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>270300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>331500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>234200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>232600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>263400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>254200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>265400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>266300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>265800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>282900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>261200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>364700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,112 +7798,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>4200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>593700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>580900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>580700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>634400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>555800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>393400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>392200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>396600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>401800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>416000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>411800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>415800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>415900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>415300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>419100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>425800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>428500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>415300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>422100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>425500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>428200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>431000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>438900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>442800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>438200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1284300</v>
+      </c>
+      <c r="E89" s="3">
         <v>1367800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1408800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1375700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1399600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1305200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1193200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1363400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1550600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1111900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1171900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1336600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1734500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>787800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>771200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>400400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>652500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>541000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>307900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>628900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>768300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>817100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>774500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>745700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>778400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>716700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>607300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>738000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>724300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>817200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>797200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>801500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>935200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,112 +8586,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1627800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1733700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-944700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-685000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-975800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-312900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-19500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-99100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-146100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-98600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-61300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-354100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-436100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-298900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-280300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-659200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1372600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-850700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-841800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-628600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-303100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-973200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-453600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-844200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-216100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-646600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-187300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-302600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>69300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-220800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>70000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-326200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-235200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-714600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-910900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-546100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-783200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,19 +9053,20 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E96" s="3">
         <v>48000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>41800</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
@@ -8847,8 +9080,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8925,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,316 +9479,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3172800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2344500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-431600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-872700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>289000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-166500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-579700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-600300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-403700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-897800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>21683500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-660400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-550600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-288700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>270100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3189500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>48700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>321700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1197100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>965800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>212800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>928800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="N101" s="3">
-        <v>500</v>
       </c>
       <c r="O101" s="3">
         <v>500</v>
       </c>
       <c r="P101" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-400</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2552900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2342300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>126700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-340000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-781200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1289700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>53300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-493100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-145700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>56200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-568500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>380200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-58900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-82100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>180200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>882700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3582200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>103700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>226300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1159200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>6300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>428000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>205400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2077000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2072300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1948100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1958100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2018100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1898600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1891700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1924400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1865700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1707600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1654800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1635500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1786700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1417600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1416800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1209600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1090600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1017500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1019400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1187300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1179800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1208300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1153600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1203100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1183500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>740500</v>
+      </c>
+      <c r="E9" s="3">
         <v>871300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>927800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>809200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>782100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>766700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>789000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>844800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>836500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>260900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>161400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>193200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>208100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>162000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>53500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>39200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>75300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>51200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>52200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>94700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>86900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>44100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>65200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>91700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>125900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>84800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>103300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>132500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>141200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>137800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>136300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>122400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>143300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1336600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1201000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1020300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1148900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1236000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1132000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1102700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1079500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1029200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1446700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1493400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1442300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1578600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1255600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1363300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1150600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1051400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>942200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>968200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1135100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1085100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1121400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1109500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1137900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1091800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>997300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1180,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,222 +1398,231 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-146800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-9300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>52900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-33600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-572700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-634900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-5800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>21900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2749700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>146000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>153000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>126300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>53200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>118500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1015800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>98800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>22500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>16100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>31200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>17800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>14000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>10400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>45600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>10000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>19700</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
         <v>8000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>593700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>580900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>580700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>634400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>555800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>393400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>392200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>396600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>401800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>416000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>411800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>415800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>415900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>415300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>419100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>425800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>425900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>412700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>417700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>422700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>425400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>428300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>435000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>438500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>433500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>853600</v>
+      </c>
+      <c r="E17" s="3">
         <v>994300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1049100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>934500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>901400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>888500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>900900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>964600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>947100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>951700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>864400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>900800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3689600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>983100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>668000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>650500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>546300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>659300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1543900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>615700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>597600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>590200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>555300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>566700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>589500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>637800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>573800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>620300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>643100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>673200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>695700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>666000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>654300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>693300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1223500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1078000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>899000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1023600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1116700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1010100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>990800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>959800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>918600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>756000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>790400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>734700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>434500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>748800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>559100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>544300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>358200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-524500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>571600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>582200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>618100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>598300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>636400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>594000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>541100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>572700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>523100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>486700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>541300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>514500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>528200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>535200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>616600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,543 +1917,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-37900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-43600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-43800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-32100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-39500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-58800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-41000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-34400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-32500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>123700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>61400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>22700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>27200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>39800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>22500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-121200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>21800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>45800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>107400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>37100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>68400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>19900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>25000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>55800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>105900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>51900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>61700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>60500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>77200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1269200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1129600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>950600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1063800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1164200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1077000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1041000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1002400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>959400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1473300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1432800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1338200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1017500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1181900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>973700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>943100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>745000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-229700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1005200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1043800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1141400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1050800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1123800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1025500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>989500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>502900</v>
+      </c>
+      <c r="E22" s="3">
         <v>504700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>516300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>478300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>491500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>495900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>447000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>427400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>436200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>420300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>390800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>380800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>369500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>287200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>292900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>280800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>310500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>307300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>309700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>306100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>374900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>308900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>322600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>318300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>301800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>297000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>289400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>291000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>274900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>278200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>266000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>279200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>271300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>753800</v>
+      </c>
+      <c r="E23" s="3">
         <v>763700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>435800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>524500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>698300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1145700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1219700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>572600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>500900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>459300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>461100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>357500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>92200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>501300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>288700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>265800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>32700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-953000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>283700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>321900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>350600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>326500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>382100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>281400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>259200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>300700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>289500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>301600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>318300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>298000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>322700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>296800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>422600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>111000</v>
+      </c>
+      <c r="E24" s="3">
         <v>92500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>60700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>76300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>94100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>110700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>75700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>65600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>50000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-278300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>62100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>40500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>39900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-106100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>38300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>43500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>39000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>42400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>49700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>28100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>39100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>37600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>39200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>34200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>42000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>38600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>60700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E26" s="3">
         <v>671200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>375000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>448200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>604200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1106700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1109000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>496900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>435300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>459500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>396800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>307400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>72100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>439200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>248200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>225900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-846900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>245400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>278500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>311600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>284100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>332500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>244800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>231000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>261600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>251900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>262400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>290300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>263900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>280800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>258300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>361900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E27" s="3">
         <v>671200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>375000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>448200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>604200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1105800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1105300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>492900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>432100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>495000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>440000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>339800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>88800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>433900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>249800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>228000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>28500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-849900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>246100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>276800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>309800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>270300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>331500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>234200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>232600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>263400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>254200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>265400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>288300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>265800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>282900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>261200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>364700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2918,8 +2979,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2936,11 +2997,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E32" s="3">
         <v>43600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>43800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>32100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>39500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>58800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>41000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>34400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>32500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-123700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-61400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-22700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-39800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-22500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>121200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-21800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-45800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-107400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-68400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E33" s="3">
         <v>671200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>375000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>448200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>604200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1105800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1105300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>492900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>432100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>495000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>440000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>339800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>88800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>433900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>249800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>228000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>28500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-849900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>246100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>276800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>309800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>270300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>331500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>234200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>232600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>263400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>254200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>265400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>266300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>265800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>282900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>261200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>364700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E35" s="3">
         <v>671200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>375000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>448200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>604200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1105800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1105300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>492900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>432100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>495000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>440000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>339800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>88800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>433900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>249800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>228000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>28500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-849900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>246100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>276800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>309800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>270300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>331500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>234200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>232600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>263400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>254200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>265400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>266300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>265800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>282900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>261200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>364700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,145 +3872,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1056500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1209200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3754500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1436000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1292000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1627200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2415300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1153900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1089000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1597100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1098500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1229000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1185700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1728800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1311200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1402900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1447500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1248800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3244400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2382700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4693900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1121400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1036900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>782900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2348100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E42" s="3">
         <v>81800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>55700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>143500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>153200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>130600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>244500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>220600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>175700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4000,159 +4090,165 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2843900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3449600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3484300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3211000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3829100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3832200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3674200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3650900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3445600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>593300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>487100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>469400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>567100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>636500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>647200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>525400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>349000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>343200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>428900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>419800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>279200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>403400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>330400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>276000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>241200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>260700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>335500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>266700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>286000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>425800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>301900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>259600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>218100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>253700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>109600</v>
+      </c>
+      <c r="E44" s="3">
         <v>90900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>80000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>62500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>72900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>85700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>76800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>72600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>59200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>55900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>43000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>53400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>51900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>48600</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
@@ -4169,190 +4265,196 @@
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
         <v>3200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>6400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>57200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>20300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>31000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>55000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>37100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>37000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>39000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>42300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>46900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>59400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>52700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>524600</v>
+      </c>
+      <c r="E45" s="3">
         <v>466200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>520900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>104900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>459100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>296700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>420600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>808500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>607500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4522400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5346400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5234800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5056500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5039100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2070100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2078600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2421700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2237200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2800500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3465400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3212200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3052900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3012300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3038300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3069700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4794400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5490100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8095200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5134100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5999900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6170700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7022800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6069600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5551600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4428,329 +4530,341 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1250200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1205700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1162800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1117700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1107300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1058600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1011200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>968500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>914200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3067400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3630300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3732400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3859700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2994700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1443300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1506000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1578100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1545700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1631300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1728600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1276600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1222600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1247600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1187800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1181300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>974200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>916700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>898000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E48" s="3">
         <v>46000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>61000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>66500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>57000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>60700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>70600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>75800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>55302800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>54751400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>54433800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>54686500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>57946300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34465600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34797100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34626000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>35219600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>34799600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>35422400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35738700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35940500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35303800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35329900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35159700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2263200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2403300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2566600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2698900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2894400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3045200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3176900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3310800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3494300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3549700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3800700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3974100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4118300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4653400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>802300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>828200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>850000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>874500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>912900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1031500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1076100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1117000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1230000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1276200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1381400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63941200</v>
+      </c>
+      <c r="E52" s="3">
         <v>62036000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>61659400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61816200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60766400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60667400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>60120700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59302700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59433700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>662800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>267800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>347200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>439800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>611900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>537500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>368000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>399900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>378100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>390400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>513200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>626300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>610600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1113800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>846300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1002600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>533400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>827300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>656000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>747400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>735900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>652000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>72555500</v>
+      </c>
+      <c r="E54" s="3">
         <v>71442000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73824900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71106700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71105000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71274600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71593700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>69928400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69684400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69726900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69811200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69747600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>70208200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>74569800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41499300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41824100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>42065000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42048000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>44421100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>45193800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>47144800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43749200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43549000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43067900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>44717000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,145 +5492,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>478600</v>
+      </c>
+      <c r="E57" s="3">
         <v>465700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>423300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>420600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>429400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>444000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>430000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>475300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>582000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>475200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>711100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>730700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>750800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>850200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>263600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>281300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>243700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>222200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>223100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>220100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>240400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>239100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>233400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>245800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>272000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>294300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>274900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>283900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>303900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>307400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>288100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>295500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>302400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>330400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E58" s="3">
         <v>44000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>80500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>64000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>80800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>44500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>62500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5531,23 +5665,23 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-      <c r="W58" s="3" t="s">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>11700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AB58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC58" s="3" t="s">
         <v>8</v>
@@ -5558,8 +5692,8 @@
       <c r="AE58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AF58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG58" s="3">
         <v>0</v>
@@ -5576,8 +5710,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5605,116 +5742,119 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>3782000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3535700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3578300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3512900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4200400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2329700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2566800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2650700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2670700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2697700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2876000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3186500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3244500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3336800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3326300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3413000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4245100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4084000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3848600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3889600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3737200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3530100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3400800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3480500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5790,222 +5930,231 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46229000</v>
+      </c>
+      <c r="E61" s="3">
         <v>45321800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>48418000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>45759800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45785300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>46576000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>47581200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46343800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46381700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>46533000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47350100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47927900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>48912900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50204700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>27539700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>28098600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28553100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28742100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>31087100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>30683900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>32760800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>29474500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29280000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29014200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>30750100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1144300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1092600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1050400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1007900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1063100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1018700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>945900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>876600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>845000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2194100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1925700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1859500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1807600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2085200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1054900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>996000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>954000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>913400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>884100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>990300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>950200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>910300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>935800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>892200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>842100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>804600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>789900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>750500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>712400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>673900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>685900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>655900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>615300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>579000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55363200</v>
+      </c>
+      <c r="E66" s="3">
         <v>54257100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57072400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>54090200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54149200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54685500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>55221500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>53537900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53560800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53609400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>54243500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54713200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>55555100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>57999000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31644400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>32440600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32925600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>33183600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35609700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35559800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>37761900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34434300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34374100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34054900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35810800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13351300</v>
+      </c>
+      <c r="E72" s="3">
         <v>12755800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12129400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11802200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11407200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10802600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9703300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8598000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8104800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7674900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7181000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6741800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6408100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8410300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8322600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7888700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7625700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7399700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7380700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8232500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7986100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7734600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7424100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7157200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6825300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17192100</v>
+      </c>
+      <c r="E76" s="3">
         <v>17184600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16752300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17016200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16955600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16588800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16293700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16311900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16045400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16117500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15567700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15034400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14653100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16570700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9855000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9383500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9139300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8864500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8811400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9634000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9382900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9314900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9174900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9013000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8906200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>642900</v>
+      </c>
+      <c r="E81" s="3">
         <v>671200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>375000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>448200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>604200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1105800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1105300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>492900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>432100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>495000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>440000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>339800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>88800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>433900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>249800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>228000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>28500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-849900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>246100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>276800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>309800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>270300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>331500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>234200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>232600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>263400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>254200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>265400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>266300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>265800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>282900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>261200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>364700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E83" s="3">
         <v>3100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>593700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>580900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>580700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>634400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>555800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>393400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>392200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>396600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>401800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>416000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>411800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>415800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>415900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>415300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>419100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>425800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>428500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>415300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>422100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>425500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>428200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>431000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>438900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>442800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>438200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1284300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1367800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1408800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1375700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1399600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1305200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1193200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1363400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1550600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1111900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1171900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1336600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1734500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>787800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>771200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>400400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>652500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>541000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>307900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>628900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>768300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>817100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>774500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>745700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>778400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>716700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>607300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>738000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>724300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>817200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>797200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>801500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>935200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2500800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1627800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1733700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-944700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-685000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-975800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-312900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-99100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-146100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-98600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-61300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-354100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-436100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-298900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-280300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2005200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-659200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1372600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-850700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-841800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-628600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-303100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-973200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-453600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-844200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-216100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-646600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-187300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-302600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>69300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-220800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>70000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-326200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-235200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-714600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-910900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-546100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-783200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,22 +9287,23 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E96" s="3">
         <v>50200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>48000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>41800</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
@@ -9083,8 +9317,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9161,8 +9395,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>534500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3172800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2344500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-431600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-872700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>289000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-166500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-579700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-600300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-403700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-897800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>21683500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-660400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-550600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-288700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>270100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3189500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>48700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>321700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1197100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>965800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>212800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>928800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E101" s="3">
         <v>2400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="O101" s="3">
-        <v>500</v>
       </c>
       <c r="P101" s="3">
         <v>500</v>
       </c>
       <c r="Q101" s="3">
+        <v>500</v>
+      </c>
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-132300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2552900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2342300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>126700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-340000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-781200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1289700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>53300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-493100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-145700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>56200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-568500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>380200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-58900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-82100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>180200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>882700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3582200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>103700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>226300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1159200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>428000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>205400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,493 +656,506 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1886800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2077000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2072300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1948100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1958100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2018100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1898600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1891700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1924400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1865700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1707600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1654800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1635500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1786700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1417600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1416800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1209600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1090600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1017500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1019400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1187300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1179800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1208300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1153600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1203100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1183500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>763500</v>
+      </c>
+      <c r="E9" s="3">
         <v>740500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>871300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>927800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>809200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>782100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>766700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>789000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>844800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>836500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>260900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>161400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>193200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>208100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>162000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>53500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>39200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>75300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>51200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>52200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>94700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>86900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>44100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>65200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>91700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>125900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>84800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>103300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>132500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>141200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>137800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>136300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>122400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>143300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1123300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1336600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1201000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1020300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1148900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1236000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1132000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1102700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1079500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1029200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1446700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1493400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1442300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1578600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1255600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1363300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1150600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1051400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>942200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>968200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1135100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1085100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1121400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1109500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1137900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1091800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>997300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,8 +1194,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,8 +1305,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,228 +1418,237 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-945900</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-146800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-9300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>52900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-33600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-572700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-634900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-5800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>16700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>21900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2749700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>146000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>153000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>126300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>53200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>118500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1015800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>98800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>22500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>31200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>17800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>12800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>14000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>10400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>45600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>9900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>19700</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E15" s="3">
         <v>7800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>593700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>580900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>580700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>634400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>555800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>393400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>392200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>396600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>401800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>416000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>411800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>415800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>415900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>415300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>419100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>425800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>425900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>412700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>417700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>422700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>425400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>428300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>435000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>438500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>433500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1684,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>934300</v>
+      </c>
+      <c r="E17" s="3">
         <v>853600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>994300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1049100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>934500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>901400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>888500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>900900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>964600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>947100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>951700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>864400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3689600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>983100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>668000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>650500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>546300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>659300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1543900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>615700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>597600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>590200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>555300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>566700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>589500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>637800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>573800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>620300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>643100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>673200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>695700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>666000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>654300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>693300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>952500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1223500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1078000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>899000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1023600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1116700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1010100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>990800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>959800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>918600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>756000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>790400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>734700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>434500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>748800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>559100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>544300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>358200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-524500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>571600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>582200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>618100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>598300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>636400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>594000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>541100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>572700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>523100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>486700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>541300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>514500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>528200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>535200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>616600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,558 +1951,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-48100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-37900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-43600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-43800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-32100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-39500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-58800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-41000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-34400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>123700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>61400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>22700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>39800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>22500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-15000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-121200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>21800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>45800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>107400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>37100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>68400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>19900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>55800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>105900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>51900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>61700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>60500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>40800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>77200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1008800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1269200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1129600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>950600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1063800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1164200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1077000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1041000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1002400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>959400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1473300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1432800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1338200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1017500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1181900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>973700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>943100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>745000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-229700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1005200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1043800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1141400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1050800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1123800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1025500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>989500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>518900</v>
+      </c>
+      <c r="E22" s="3">
         <v>502900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>504700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>516300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>478300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>491500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>495900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>447000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>427400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>436200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>420300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>390800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>380800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>369500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>287200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>292900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>280800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>310500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>307300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>309700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>306100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>374900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>308900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>322600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>318300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>301800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>297000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>289400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>291000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>274900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>278200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>266000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>279200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>271300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1427600</v>
+      </c>
+      <c r="E23" s="3">
         <v>753800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>763700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>435800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>524500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>698300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1145700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1219700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>572600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>459300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>461100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>357500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>92200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>501300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>288700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>265800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-953000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>283700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>321900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>350600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>326500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>382100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>281400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>259200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>300700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>289500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>301600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>318300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>298000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>322700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>296800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>422600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>168400</v>
+      </c>
+      <c r="E24" s="3">
         <v>111000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>92500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>60700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>76300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>94100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>110700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>75700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>65600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>50000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-278300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>62100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>40500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>39900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-106100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>38300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>39000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>49700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>36600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>28100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>39100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>39200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>28000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>34200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>38600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>60700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2627,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1259200</v>
+      </c>
+      <c r="E26" s="3">
         <v>642900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>671200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>375000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>448200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>604200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1106700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1109000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>496900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>435300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>459500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>396800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>307400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>72100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>439200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>248200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>225900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>25600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-846900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>245400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>278500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>311600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>284100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>332500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>244800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>231000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>261600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>251900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>262400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>290300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>263900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>280800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>258300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>361900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1259200</v>
+      </c>
+      <c r="E27" s="3">
         <v>642900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>671200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>375000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>448200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>604200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1105800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1105300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>492900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>432100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>495000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>440000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>339800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>88800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>433900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>249800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>228000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>28500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-849900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>246100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>276800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>309800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>270300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>331500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>234200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>232600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>263400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>254200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>265400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>288300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>265800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>282900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>261200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>364700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2966,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2982,8 +3043,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3000,11 +3061,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3018,8 +3079,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3192,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,228 +3305,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E32" s="3">
         <v>37900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>43600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>43800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>32100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>39500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>58800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>41000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>34400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-123700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-61400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-22700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-39800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-22500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>15000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>121200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-21800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-45800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-107400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-68400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1259200</v>
+      </c>
+      <c r="E33" s="3">
         <v>642900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>671200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>375000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>448200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>604200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1105800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1105300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>492900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>432100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>495000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>440000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>339800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>88800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>433900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>249800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>228000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>28500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-849900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>246100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>276800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>309800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>270300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>331500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>234200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>232600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>263400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>254200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>265400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>266300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>265800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>282900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>261200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>364700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3644,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1259200</v>
+      </c>
+      <c r="E35" s="3">
         <v>642900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>671200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>375000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>448200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>604200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1105800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1105300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>492900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>432100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>495000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>440000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>339800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>88800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>433900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>249800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>228000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>28500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-849900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>246100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>276800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>309800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>270300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>331500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>234200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>232600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>263400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>254200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>265400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>266300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>265800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>282900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>261200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>364700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3918,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,151 +3959,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2696100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1056500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1209200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3754500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1436000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1292000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1627200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2415300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1153900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1089000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1597100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1098500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1229000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1185700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1728800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1311200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1402900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1447500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1248800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3244400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2382700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4693900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1121400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1036900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>782900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2348100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E42" s="3">
         <v>47000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>81800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>55700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>143500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>153200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>130600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>244500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>220600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>175700</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4093,165 +4183,171 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2744700</v>
+      </c>
+      <c r="E43" s="3">
         <v>2843900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3449600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3484300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3211000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3829100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3832200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3674200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3650900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3445600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>593300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>487100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>469400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>567100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>636500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>647200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>525400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>349000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>343200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>428900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>419800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>279200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>403400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>330400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>276000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>241200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>260700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>335500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>266700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>286000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>425800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>301900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>259600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>218100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>253700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>116200</v>
+      </c>
+      <c r="E44" s="3">
         <v>109600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>90900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>80000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>62500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>72900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>76800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>72600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>59200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>55900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>43000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>53400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>51900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>48600</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
@@ -4268,196 +4364,202 @@
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
         <v>3200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>57200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>20300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>31000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>55000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>37100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>37000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>39000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>42300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>59400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>52700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>469600</v>
+      </c>
+      <c r="E45" s="3">
         <v>524600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>466200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>520900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>104900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>459100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>296700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>420600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>808500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>607500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4522400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5346400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5234800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5056500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5039100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2070100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2078600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2421700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2237200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2800500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3465400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3212200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3052900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3012300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3038300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3069700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6213500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4794400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5490100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8095200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5134100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5999900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6170700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7022800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6069600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5551600</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4533,338 +4635,350 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1232100</v>
+      </c>
+      <c r="E47" s="3">
         <v>1250200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1205700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1162800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1117700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1107300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1058600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1011200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>968500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>914200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3067400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3630300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3732400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3859700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2994700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1443300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1506000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1578100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1545700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1631300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1728600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1276600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1222600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1247600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1187800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1181300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>974200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>916700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>898000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E48" s="3">
         <v>43700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>61000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>57000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>60700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>70600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>75800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55302800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>54751400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>54433800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>54686500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>57946300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>34465600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>34797100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34626000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35219600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34799600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35422400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35738700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35940500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35303800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35329900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35159700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2153400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2263200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2403300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2566600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2698900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2894400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3045200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3176900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3310800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3494300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3549700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3800700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3974100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4118300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4653400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>802300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>828200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>850000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>874500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>912900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1031500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1076100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1117000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1230000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1276200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1381400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5087,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5200,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63732400</v>
+      </c>
+      <c r="E52" s="3">
         <v>63941200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62036000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61659400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>61816200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>60766400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>60667400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>60120700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59302700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59433700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>662800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>267800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>347200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>439800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>611900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>537500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>368000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>399900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>378100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>390400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>513200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>626300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>610600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1113800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>846300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1002600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>533400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>827300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>656000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>747400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>735900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>652000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5426,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73633900</v>
+      </c>
+      <c r="E54" s="3">
         <v>72555500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71442000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73824900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71106700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71105000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71274600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71593700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>69928400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>69684400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69726900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69811200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69747600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>70208200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>74569800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>41499300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41824100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>42065000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>42048000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>44421100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>45193800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>47144800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>43749200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43549000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43067900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>44717000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5582,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,151 +5623,155 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>488000</v>
+      </c>
+      <c r="E57" s="3">
         <v>478600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>465700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>423300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>420600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>429400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>444000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>430000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>475300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>582000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>475200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>711100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>730700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>750800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>850200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>263600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>281300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>243700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>222200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>223100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>220100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>240400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>239100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>233400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>245800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>272000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>294300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>274900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>283900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>303900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>307400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>288100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>295500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>302400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>330400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E58" s="3">
         <v>63600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>80500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>64000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>62500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5668,23 +5802,23 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AC58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD58" s="3" t="s">
         <v>8</v>
@@ -5695,8 +5829,8 @@
       <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3">
-        <v>0</v>
+      <c r="AG58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -5713,8 +5847,11 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5745,119 +5882,122 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>3782000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3535700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3578300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3512900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4200400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2329700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2566800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2650700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2670700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2697700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2876000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3186500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3244500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3336800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3326300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3413000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4454100</v>
+      </c>
+      <c r="E60" s="3">
         <v>4300900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4245100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4084000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3848600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3889600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3737200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3530100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3480500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5933,228 +6073,237 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46156400</v>
+      </c>
+      <c r="E61" s="3">
         <v>46229000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>45321800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>48418000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>45759800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45785300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>46576000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47581200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46343800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>46381700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>46533000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>47350100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>47927900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48912900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50204700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>27539700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>28098600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>28553100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28742100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>31087100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30683900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>32760800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>29474500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29280000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>29014200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>30750100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1207400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1144300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1092600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1050400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1007900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1063100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1018700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>945900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>876600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>845000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2194100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1925700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1859500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1807600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2085200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1054900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>996000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>954000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>913400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>884100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>990300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>950200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>910300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>935800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>892200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>842100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>804600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>789900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>750500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>712400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>673900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>685900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>655900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>615300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>579000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6412,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6525,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6638,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55686700</v>
+      </c>
+      <c r="E66" s="3">
         <v>55363200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>54257100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>57072400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54090200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54149200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54685500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>55221500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>53537900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>53560800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53609400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>54243500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>54713200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>55555100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>57999000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31644400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>32440600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>32925600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>33183600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>35609700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>35559800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>37761900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>34434300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>34374100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34054900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>35810800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6794,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6905,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7018,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7131,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7244,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14563600</v>
+      </c>
+      <c r="E72" s="3">
         <v>13351300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12755800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12129400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11802200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11407200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10802600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9703300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8598000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8104800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7674900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7181000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6741800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6408100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8410300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8322600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7888700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7625700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7399700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7380700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8232500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7986100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7734600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7424100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7157200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6825300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7470,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7583,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7696,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17947100</v>
+      </c>
+      <c r="E76" s="3">
         <v>17192100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17184600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16752300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17016200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16955600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16588800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16293700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16311900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16045400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16117500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15567700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15034400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14653100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16570700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9855000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9383500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9139300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8864500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8811400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9634000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>9382900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9314900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9174900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9013000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8906200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7922,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1259200</v>
+      </c>
+      <c r="E81" s="3">
         <v>642900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>671200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>375000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>448200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>604200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1105800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1105300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>492900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>432100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>495000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>440000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>339800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>88800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>433900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>249800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>228000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>28500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-849900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>246100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>276800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>309800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>270300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>331500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>234200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>232600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>263400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>254200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>265400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>266300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>265800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>282900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>261200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>364700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,118 +8196,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>593700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>580900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>580700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>634400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>555800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>393400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>392200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>396600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>401800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>416000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>411800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>415800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>415900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>415300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>419100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>425800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>428500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>415300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>422100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>425500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>428200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>431000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>438900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>442800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>438200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8420,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8533,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8646,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8759,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8872,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1331400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1335000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1284300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1367800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1408800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1375700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1399600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1305200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1193200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1363400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1550600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1111900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1171900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1336600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1734500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>787800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>771200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>400400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>652500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>541000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>307900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>628900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>768300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>817100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>774500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>745700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>778400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>716700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>607300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>738000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>724300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>817200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>797200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>801500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>935200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,118 +9028,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-470100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2500800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1627800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1733700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-944700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-685000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-975800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-312900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-99100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-146100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-98600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-354100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-436100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-298900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-280300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9252,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9365,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>706200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2005200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-659200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1372600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-850700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-841800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-628600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-303100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-973200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-453600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-844200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-216100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-646600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-187300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-302600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>69300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-220800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>70000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-326200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-235200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-714600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-910900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-546100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-783200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,25 +9521,26 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E96" s="3">
         <v>5600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>50200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>48000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>41800</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
@@ -9320,8 +9554,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9398,8 +9632,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9745,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9858,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,334 +9971,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-460600</v>
+      </c>
+      <c r="E100" s="3">
         <v>534500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3172800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2344500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-431600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-872700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>289000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-166500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-579700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-600300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-403700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-897800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>21683500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-660400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-550600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-288700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>270100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3189500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>48700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>321700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1197100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>965800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>212800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>928800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="P101" s="3">
-        <v>500</v>
       </c>
       <c r="Q101" s="3">
         <v>500</v>
       </c>
       <c r="R101" s="3">
+        <v>500</v>
+      </c>
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1576900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-132300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2552900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2342300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>126700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-340000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-781200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1289700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-493100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-145700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>56200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-568500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>380200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-58900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-82100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>180200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>882700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3582200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>103700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>226300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1159200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>6300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>428000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>205400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2244300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2308600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1886800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2077000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2072300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1948100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1958100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2018100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1898600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1891700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1924400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1865700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1707600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1654800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1635500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1786700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1417600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1416800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1209600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1090600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1017500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1019400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1187300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1179800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1208300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1153600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1203100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1183500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1032800</v>
+      </c>
+      <c r="E9" s="3">
         <v>758000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>763500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>740500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>871300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>927800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>809200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>782100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>766700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>789000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>844800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>836500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>260900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>161400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>193200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>208100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>162000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>53500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>59000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>39200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>75300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>51200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>52200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>94700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>86900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>44100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>65200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>91700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>125900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>84800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>103300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>132500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>141200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>137800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>136300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>122400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>143300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1211600</v>
+      </c>
+      <c r="E10" s="3">
         <v>1550500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1123300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1336600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1201000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1020300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1148900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1236000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1132000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1102700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1079500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1029200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1446700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1493400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1442300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1578600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1255600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1363300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1150600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1051400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>942200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>968200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1135100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1085100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1121400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1109500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1137900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1091800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>997300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1209,8 +1221,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1325,8 +1338,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1441,240 +1457,249 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1184600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-430800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-945900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-146800</v>
-      </c>
       <c r="H14" s="3">
+        <v>-124100</v>
+      </c>
+      <c r="I14" s="3">
         <v>-9300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>52900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-33600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-572700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-634900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-5800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>21900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2749700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>146000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>153000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>126300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>53200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>118500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1015800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>98800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>31200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>17800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>12800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>14000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>2100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>45600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>10000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>9900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>19700</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E15" s="3">
         <v>8700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>9200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>593700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>580900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>580700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>634400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>555800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>393400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>392200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>396600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>401800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>416000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>411800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>415800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>415900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>415300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>419100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>425800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>425900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>412700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>417700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>422700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>425400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>428300</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>435000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>438500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>433500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1712,240 +1737,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1165900</v>
+      </c>
+      <c r="E17" s="3">
         <v>886900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>934300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>853600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>994300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1049100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>934500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>901400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>888500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>964600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>947100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>951700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>864400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>900800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3689600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>983100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>668000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>650500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>546300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>659300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1543900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>615700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>597600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>590200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>555300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>566700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>589500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>637800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>573800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>620300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>643100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>673200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>695700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>666000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>654300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>693300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1078400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1421700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>952500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1223500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1078000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>899000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1023600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1116700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1010100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>990800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>959800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>918600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>756000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>790400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>734700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>434500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>748800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>559100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>544300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>358200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-524500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>571600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>582200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>618100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>598300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>636400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>594000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>541100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>572700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>523100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>486700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>541300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>514500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>528200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>535200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>616600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1986,588 +2018,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1290900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-47500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-48100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-37900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-43600</v>
-      </c>
       <c r="H20" s="3">
+        <v>-66300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-43800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-32100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-39500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-58800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-41000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-34400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-32500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>123700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>61400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>22700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>27200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>39800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>22500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-15000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-121200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>45800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>107400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>37100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>68400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>19900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>25000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>55800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>105900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>51900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>61700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>60500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>40800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>77200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2378200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1477800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1008800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1269200</v>
       </c>
-      <c r="G21" s="3">
-        <v>1129600</v>
-      </c>
       <c r="H21" s="3">
+        <v>1152300</v>
+      </c>
+      <c r="I21" s="3">
         <v>950600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1063800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1164200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1077000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1041000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1002400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>959400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1473300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1432800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1338200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1017500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1181900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>973700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>943100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>745000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-229700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1005200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1043800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1141400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1050800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1123800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1025500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>989500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>474300</v>
+      </c>
+      <c r="E22" s="3">
         <v>485900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>518900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>502900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>504700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>516300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>478300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>491500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>495900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>447000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>427400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>436200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>420300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>390800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>380800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>369500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>287200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>292900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>280800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>310500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>307300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>309700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>306100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>374900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>308900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>322600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>318300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>301800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>297000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>289400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>291000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>274900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>278200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>266000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>279200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>271300</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>710500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1414000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1427600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>753800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>763700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>435800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>524500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>698300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1145700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1219700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>572600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>459300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>461100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>357500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>92200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>501300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>288700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>265800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>32700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-953000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>283700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>321900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>350600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>326500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>382100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>281400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>259200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>289500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>301600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>318300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>298000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>322700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>296800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>422600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>77700</v>
+      </c>
+      <c r="E24" s="3">
         <v>198200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>168400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>111000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>92500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>60700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>76300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>94100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>110700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>75700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>65600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>64300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-278300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>20000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>62100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>40500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>39900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-106100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>38300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>43500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>39000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>42400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>36600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>39100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>37600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>39200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>28000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>34200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>42000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>38600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>60700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2682,240 +2730,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>632800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1215700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1259200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>642900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>671200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>375000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>448200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>604200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1106700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1109000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>496900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>435300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>459500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>396800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>307400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>72100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>439200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>248200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>225900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-846900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>245400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>278500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>311600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>284100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>332500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>244800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>231000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>261600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>251900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>262400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>290300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>263900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>280800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>258300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>361900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>632800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1215700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1259200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>642900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>671200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>375000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>448200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>604200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1105800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1105300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>492900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>432100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>495000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>440000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>339800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>88800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>433900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>249800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>228000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>28500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-849900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>246100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>276800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>309800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>270300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>331500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>234200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>232600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>263400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>254200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>265400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>288300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>265800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>282900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>261200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>364700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3030,8 +3087,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3110,8 +3170,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3128,11 +3188,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3146,8 +3206,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3262,8 +3325,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3378,240 +3444,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1290900</v>
+      </c>
+      <c r="E32" s="3">
         <v>47500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>48100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>37900</v>
       </c>
-      <c r="G32" s="3">
-        <v>43600</v>
-      </c>
       <c r="H32" s="3">
+        <v>66300</v>
+      </c>
+      <c r="I32" s="3">
         <v>43800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>32100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>39500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>58800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>41000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>34400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>32500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-123700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-61400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-22700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-27200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-39800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-22500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>15000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>121200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-45800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-107400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-37100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-68400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>632800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1215700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1259200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>642900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>671200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>375000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>448200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>604200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1105800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1105300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>492900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>432100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>495000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>440000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>339800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>88800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>433900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>249800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>228000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>28500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-849900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>246100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>276800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>309800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>270300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>331500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>234200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>232600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>263400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>254200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>265400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>266300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>265800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>282900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>261200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>364700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3726,245 +3801,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>632800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1215700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1259200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>642900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>671200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>375000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>448200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>604200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1105800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1105300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>492900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>432100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>495000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>440000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>339800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>88800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>433900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>249800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>228000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>28500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-849900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>246100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>276800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>309800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>270300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>331500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>234200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>232600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>263400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>254200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>265400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>266300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>265800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>282900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>261200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>364700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4005,8 +4089,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4047,163 +4132,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1379200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1814300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2696100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1056500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1209200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3754500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1436000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1292000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1627200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2415300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1153900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1089000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1597100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1098500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1229000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1185700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1728800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1311200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1402900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1447500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1248800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3244400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2382700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4693900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1121400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1036900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>782900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2348100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E42" s="3">
         <v>20200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>36900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>47000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>81800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>55700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>143500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>153200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>130600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>244500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>220600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>175700</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4279,177 +4368,183 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3421200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3057200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2744700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2843900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3449600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3484300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3211000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3829100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3832200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3674200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3650900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3445600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>593300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>487100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>469400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>567100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>636500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>647200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>525400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>349000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>343200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>428900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>419800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>279200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>403400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>330400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>276000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>241200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>260700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>335500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>266700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>286000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>425800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>301900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>259600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>218100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>253700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E44" s="3">
         <v>118600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>116200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>109600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>90900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>80000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>62500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>72900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>85700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>76800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>72600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>59200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>55900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>43000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>53400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>51900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>48600</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
@@ -4466,208 +4561,214 @@
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="3">
         <v>3200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>57200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>20300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>31000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>55000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>37100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>37000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>42300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>46900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>59400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>52700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1104300</v>
+      </c>
+      <c r="E45" s="3">
         <v>562000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>469600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>524600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>466200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>520900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>104900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>459100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>296700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>420600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>808500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>607500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4522400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5346400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5234800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5056500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5039100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2070100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2078600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2421700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2237200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2800500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3465400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3212200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3052900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3012300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3038300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3069700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6129900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5670400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6213500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4794400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5490100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8095200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5134100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5999900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6170700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7022800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6069600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5551600</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4743,356 +4844,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1364900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1247300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1232100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1250200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1205700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1162800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1117700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1107300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1058600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1011200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>968500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>914200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3067400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3630300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3732400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3859700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2994700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1443300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1506000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1578100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1545700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1631300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1728600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1276600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1222600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1247600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1187800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1181300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>974200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>916700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>898000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E48" s="3">
         <v>41900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>61000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>57000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>60700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>75800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>55302800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>54751400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54433800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>54686500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>57946300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>34465600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>34797100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34626000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>35219600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>34799600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>35422400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35738700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35940500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35303800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35329900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>35159700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1895600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2003200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2153400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2263200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2403300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2566600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2698900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2894400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3045200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3176900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3310800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3494300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3549700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3800700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3974100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4118300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4653400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>802300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>828200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>850000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>874500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>912900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1031500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1076100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1230000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1276200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1381400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5207,8 +5320,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5323,124 +5439,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>62069100</v>
+      </c>
+      <c r="E52" s="3">
         <v>62713300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>63732400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63941200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62036000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>61659400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61816200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>60766400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>60667400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>60120700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59302700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>59433700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>662800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>267800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>347200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>439800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>611900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>537500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>368000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>399900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>378100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>390400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>513200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>626300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>610600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1113800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>846300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1002600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>533400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>827300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>656000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>747400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>735900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>652000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5555,124 +5677,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71671800</v>
+      </c>
+      <c r="E54" s="3">
         <v>71938300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73633900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72555500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71442000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>73824900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71106700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71105000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71274600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71593700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>69928400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69684400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69726900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>69811200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>69747600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70208200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74569800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41499300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41824100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>42065000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42048000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>44421100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>45193800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>47144800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43749200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43549000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43067900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>44717000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5713,8 +5841,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5755,163 +5884,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>562800</v>
+      </c>
+      <c r="E57" s="3">
         <v>527000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>488000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>478600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>465700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>423300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>420600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>429400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>444000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>430000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>475300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>582000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>475200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>711100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>730700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>750800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>850200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>263600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>281300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>243700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>222200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>223100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>220100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>240400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>239100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>233400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>245800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>272000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>294300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>274900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>283900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>303900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>307400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>288100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>295500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>302400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>330400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E58" s="3">
         <v>78100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>95200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>63600</v>
       </c>
-      <c r="G58" s="3">
-        <v>44000</v>
-      </c>
       <c r="H58" s="3">
+        <v>15400</v>
+      </c>
+      <c r="I58" s="3">
         <v>80500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>54200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>64000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>80800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>44500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>62500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5942,23 +6075,23 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-      <c r="Z58" s="3" t="s">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>8</v>
@@ -5969,8 +6102,8 @@
       <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
+      <c r="AI58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ58" s="3">
         <v>0</v>
@@ -5987,8 +6120,11 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6025,125 +6161,128 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>3782000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3535700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3578300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3512900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2329700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2566800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2650700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2670700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2697700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2876000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3186500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3244500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3336800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3326300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3413000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4566400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4478500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4454100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4300900</v>
       </c>
-      <c r="G60" s="3">
-        <v>4245100</v>
-      </c>
       <c r="H60" s="3">
+        <v>4216600</v>
+      </c>
+      <c r="I60" s="3">
         <v>4084000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3848600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3889600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3737200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3530100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3400800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3480500</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6219,240 +6358,249 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43589800</v>
+      </c>
+      <c r="E61" s="3">
         <v>44077200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46156400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46229000</v>
       </c>
-      <c r="G61" s="3">
-        <v>45321800</v>
-      </c>
       <c r="H61" s="3">
+        <v>45350300</v>
+      </c>
+      <c r="I61" s="3">
         <v>48418000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>45759800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45785300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>46576000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>47581200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>46343800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>46381700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46533000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>47350100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>47927900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>48912900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50204700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>27539700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>28098600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28553100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28742100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>31087100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>30683900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>32760800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>29474500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>29280000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29014200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>30750100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1185000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1154400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1207400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1144300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1092600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1050400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1007900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1063100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1018700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>945900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>876600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>845000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2194100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1925700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1859500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1807600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2085200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1054900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>996000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>954000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>913400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>884100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>990300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>950200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>910300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>935800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>892200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>842100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>804600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>789900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>750500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>712400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>673900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>685900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>655900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>615300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>579000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6567,8 +6715,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6683,8 +6834,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6799,124 +6953,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53348300</v>
+      </c>
+      <c r="E66" s="3">
         <v>53788900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>55686700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55363200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>54257100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57072400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>54090200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54149200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54685500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>55221500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>53537900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53560800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53609400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>54243500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54713200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>55555100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57999000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31644400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>32440600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32925600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>33183600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>35609700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35559800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>37761900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>34434300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34374100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34054900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>35810800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6957,8 +7117,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7073,8 +7234,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7189,8 +7353,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7305,8 +7472,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7421,124 +7591,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16320600</v>
+      </c>
+      <c r="E72" s="3">
         <v>15730700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>14563600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13351300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12755800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12129400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11802200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11407200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10802600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9703300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8598000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8104800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7674900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7181000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6741800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6408100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8410300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8322600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7888700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7625700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7399700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7380700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8232500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7986100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7734600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7424100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7157200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6825300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7653,8 +7829,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7769,8 +7948,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7885,124 +8067,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18323300</v>
+      </c>
+      <c r="E76" s="3">
         <v>18149200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17947100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17192100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17184600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16752300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17016200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16955600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16588800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16293700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16311900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16045400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16117500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15567700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15034400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14653100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16570700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9855000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9383500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9139300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8864500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8811400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>9634000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9382900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9314900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9174900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9013000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>8906200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8117,245 +8305,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>632800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1215700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1259200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>642900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>671200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>375000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>448200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>604200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1105800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1105300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>492900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>432100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>495000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>440000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>339800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>88800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>433900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>249800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>228000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>28500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-849900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>246100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>276800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>309800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>270300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>331500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>234200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>232600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>263400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>254200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>265400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>266300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>265800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>282900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>261200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>364700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8396,124 +8593,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>593700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>580900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>580700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>634400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>555800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>393400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>392200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>396600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>401800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>416000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>411800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>415800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>415900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>415300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>419100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>425800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>428500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>415300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>422100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>425500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>428200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>431000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>438900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>442800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>438200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8628,8 +8829,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8744,8 +8948,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8860,8 +9067,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8976,8 +9186,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9092,124 +9305,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1220500</v>
+      </c>
+      <c r="E89" s="3">
         <v>1506200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1331400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1335000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1284300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1367800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1408800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1375700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1399600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1305200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1193200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1363400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1550600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1111900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1171900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1336600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1734500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>787800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>771200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>400400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>652500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>541000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>307900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>628900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>768300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>817100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>774500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>745700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>778400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>716700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>607300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>738000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>724300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>817200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>797200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>801500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>935200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9250,124 +9469,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2082000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1021400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-470100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2500800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1627800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1733700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-944700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-685000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-975800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-312900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-99100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-146100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-98600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-354100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-436100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-298900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-280300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9482,8 +9705,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9598,124 +9824,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-916300</v>
+      </c>
+      <c r="E94" s="3">
         <v>550800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>706200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2005200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-659200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1372600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-850700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-841800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-628600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-303100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-973200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-453600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-844200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-216100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-646600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-187300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-302600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>69300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-220800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>70000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-326200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-235200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-714600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-910900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-546100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-783200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9756,31 +9988,32 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E96" s="3">
         <v>46400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>89800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>5600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>50200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>48000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>41800</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
@@ -9794,8 +10027,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9872,8 +10105,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9988,8 +10224,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10104,8 +10343,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10220,352 +10462,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-736700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2990200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-460600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>534500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3172800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2344500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-431600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-872700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>289000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-166500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-579700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-600300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-403700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-897800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>21683500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-660400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-550600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-288700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>270100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3189500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>48700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>321700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1197100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>965800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>212800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>928800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="R101" s="3">
-        <v>500</v>
       </c>
       <c r="S101" s="3">
         <v>500</v>
       </c>
       <c r="T101" s="3">
+        <v>500</v>
+      </c>
+      <c r="U101" s="3">
         <v>1000</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-400</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-432700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-933700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1576900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-132300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2552900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2342300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>126700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-340000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-781200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1289700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-493100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>500100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-145700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>56200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-568500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>380200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-58900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-82100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>180200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>882700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3582200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>103700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>226300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1159200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>428000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>205400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-356500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AER_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>AER</t>
   </si>
@@ -656,531 +656,544 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2241700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2244300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2308600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1886800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2077000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2072300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1948100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1958100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2018100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1898600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1891700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1924400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1865700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1707600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1654800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1635500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1786700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1417600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1416800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1209600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1090600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1017500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1019400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1187300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1179800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1208300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1153600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1203100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1183500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1178900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1146500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1143400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1129800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1214500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1210200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1194200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1189500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1309900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1203700</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>749200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1032800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>758000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>763500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>740500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>871300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>927800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>809200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>782100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>766700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>789000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>844800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>836500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>260900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>161400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>193200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>208100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>162000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>53500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>59000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>39200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>75300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>51200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>52200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>94700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>86900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>44100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>65200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>91700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>125900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>84800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>103300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>132500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>141200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>137800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>136300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>122400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>143300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>128700</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1492500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1211600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1550500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1123300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1336600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1201000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1020300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1148900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1236000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1132000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1102700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1079500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1029200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1446700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1493400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1442300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1578600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1255600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1363300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1150600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1051400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>942200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>968200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1135100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1085100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1121400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1109500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1137900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1091800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1053000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1061700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1040100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>997300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1073300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1072400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1057900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1067100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1166600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1075000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,8 +1235,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1341,8 +1355,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1460,246 +1477,255 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1184600</v>
+        <v>4800</v>
       </c>
       <c r="E14" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="F14" s="3">
         <v>-430800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-945900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4600</v>
       </c>
-      <c r="H14" s="3">
-        <v>-124100</v>
-      </c>
       <c r="I14" s="3">
+        <v>-146800</v>
+      </c>
+      <c r="J14" s="3">
         <v>-9300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>52900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-33600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-572700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-634900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-5800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>16700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2749700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>146000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>153000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>126300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>53200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>118500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1015800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>98800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>31200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>17800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>12800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>14000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>10400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>45600</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>9900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>19700</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E15" s="3">
         <v>8900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>9200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>8200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>593700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>580900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>580700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>634400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>555800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>393400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>392200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>396600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>401800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>416000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>411800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>415800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>415900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>415300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>419100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>425800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>425900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>412700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>417700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>422700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>425400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>428300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>435000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>438500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>433500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>439900</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1738,246 +1764,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>875500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1165900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>886900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>934300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>853600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>994300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1049100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>934500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>901400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>888500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>900900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>964600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>947100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>951700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>864400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>900800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3689600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>983100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>668000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>650500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>546300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>659300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1543900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>615700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>597600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>590200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>555300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>566700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>589500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>637800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>573800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>620300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>643100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>673200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>695700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>666000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>654300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>693300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>693400</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1366200</v>
+      </c>
+      <c r="E18" s="3">
         <v>1078400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1421700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>952500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1223500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1078000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>899000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1023600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1116700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1010100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>990800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>959800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>918600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>756000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>790400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>734700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1902900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>434500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>748800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>559100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>544300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>358200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-524500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>571600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>582200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>618100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>598300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>636400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>594000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>541100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>572700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>523100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>486700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>541300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>514500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>528200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>535200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>616600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>510300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,603 +2052,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1290900</v>
+        <v>-62400</v>
       </c>
       <c r="E20" s="3">
+        <v>-80400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-47500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-48100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-37900</v>
       </c>
-      <c r="H20" s="3">
-        <v>-66300</v>
-      </c>
       <c r="I20" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="J20" s="3">
         <v>-43800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-32100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-39500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-58800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-41000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-34400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>123700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>61400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>22700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>3400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>27200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>39800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>22500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-121200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>45800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>107400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>37100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>68400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>19900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>25000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>55800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>105900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>51900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>61700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>60500</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>40800</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>77200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>20800</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2378200</v>
+        <v>1437200</v>
       </c>
       <c r="E21" s="3">
+        <v>1167700</v>
+      </c>
+      <c r="F21" s="3">
         <v>1477800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1008800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1269200</v>
       </c>
-      <c r="H21" s="3">
-        <v>1152300</v>
-      </c>
       <c r="I21" s="3">
+        <v>1129600</v>
+      </c>
+      <c r="J21" s="3">
         <v>950600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1063800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1164200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1077000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1041000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1002400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>959400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1473300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1432800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1338200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1265100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1017500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1181900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>973700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>943100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>745000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-229700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1005200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1043800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1141400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1050800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1123800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1025500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>989500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1013000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1001000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1018000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1021400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1007200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1027600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1018800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1132000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>975700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>467100</v>
+      </c>
+      <c r="E22" s="3">
         <v>474300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>485900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>518900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>502900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>504700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>516300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>478300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>491500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>495900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>447000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>427400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>436200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>420300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>390800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>380800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>369500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>287200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>292900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>280800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>310500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>307300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>309700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>306100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>374900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>308900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>322600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>318300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>301800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>297000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>289400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>291000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>274900</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>278200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>266000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>279200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>271300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>956700</v>
+      </c>
+      <c r="E23" s="3">
         <v>710500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1414000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1427600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>753800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>763700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>435800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>524500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>698300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1145700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1219700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>572600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>459300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>461100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>357500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2280300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>92200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>501300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>288700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>265800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-953000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>283700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>321900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>350600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>326500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>382100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>281400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>259200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>289500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>301600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>318300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>298000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>322700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>296800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>422600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>258800</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>138600</v>
+      </c>
+      <c r="E24" s="3">
         <v>77700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>198200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>111000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>92500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>60700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>76300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>94100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>110700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>75700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-278300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-106100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>43500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>39000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>42400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>36600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>39100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>37600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>28000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>34200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>42000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>38600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>60700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2733,246 +2782,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E26" s="3">
         <v>632800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1215700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1259200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>642900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>671200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>375000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>448200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>604200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1106700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1109000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>496900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>435300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>459500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>396800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>307400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2002000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>72100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>439200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>248200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>225900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-846900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>245400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>278500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>311600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>284100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>332500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>244800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>231000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>261600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>251900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>262400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>290300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>263900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>280800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>258300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>361900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>216100</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E27" s="3">
         <v>632800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1215700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1259200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>642900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>671200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>375000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>448200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>604200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1105800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1105300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>492900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>432100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>495000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>440000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>339800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2000800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>88800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>433900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>249800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>228000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>28500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-849900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>246100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>276800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>309800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>270300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>331500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>234200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>232600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>263400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>254200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>265400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>288300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>265800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>282900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>261200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>364700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3090,8 +3148,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3173,8 +3234,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3191,11 +3252,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-22000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3209,8 +3270,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3328,8 +3392,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3447,246 +3514,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1290900</v>
+        <v>62400</v>
       </c>
       <c r="E32" s="3">
+        <v>80400</v>
+      </c>
+      <c r="F32" s="3">
         <v>47500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>48100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>37900</v>
       </c>
-      <c r="H32" s="3">
-        <v>66300</v>
-      </c>
       <c r="I32" s="3">
+        <v>43600</v>
+      </c>
+      <c r="J32" s="3">
         <v>43800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>32100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>39500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>58800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>41000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>34400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-123700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-61400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-22700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-3400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-27200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-39800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-22500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>15000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>121200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-45800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-107400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-37100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-68400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-19900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-55800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-105900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-51900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-61700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-60500</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-40800</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-77200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-20800</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E33" s="3">
         <v>632800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1215700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1259200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>642900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>671200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>375000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>448200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>604200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1105800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1105300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>492900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>432100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>495000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>440000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>339800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2000800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>88800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>433900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>249800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>228000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>28500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-849900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>246100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>276800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>309800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>270300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>331500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>234200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>232600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>263400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>254200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>265400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>266300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>265800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>282900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>261200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>364700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3804,251 +3880,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E35" s="3">
         <v>632800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1215700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1259200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>642900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>671200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>375000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>448200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>604200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1105800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1105300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>492900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>432100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>495000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>440000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>339800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2000800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>88800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>433900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>249800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>228000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>28500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-849900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>246100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>276800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>309800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>270300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>331500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>234200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>232600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>263400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>254200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>265400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>266300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>265800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>282900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>261200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>364700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4090,8 +4175,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4133,169 +4219,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1479700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1379200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1814300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2696100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1056500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1209200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3754500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1436000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1292000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1627200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2415300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1153900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1089000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1597100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1098500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1229000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1185700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1728800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1311200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1402900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1447500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1248800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3244400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2382700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4693900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1121400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1036900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>782900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2348100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1204000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1176000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1598500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2152200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1659700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1454200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1601100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1935600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2035400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2228000</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E42" s="3">
         <v>12200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>20200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>36900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>47000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>81800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>143500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>153200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>130600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>244500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>220600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>175700</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4371,183 +4461,189 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3485500</v>
+      </c>
+      <c r="E43" s="3">
         <v>3421200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3057200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2744700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2843900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3449600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3484300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3211000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3829100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3832200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3674200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3650900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3445600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>593300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>487100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>469400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>567100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>636500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>647200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>525400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>349000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>343200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>428900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>419800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>279200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>403400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>330400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>276000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>241200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>260700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>335500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>266700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>286000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>425800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>301900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>259600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>218100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>253700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E44" s="3">
         <v>112400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>118600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>116200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>109600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>90900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>80000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>62500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>72900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>85700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>76800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>72600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>59200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>55900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>43000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>53400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>51900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>48600</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V44" s="3" t="s">
         <v>8</v>
@@ -4564,214 +4660,220 @@
       <c r="Z44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
         <v>3200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>57200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>20300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>31000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>55000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>37100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>37000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>39000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>42300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>46900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>59400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>52700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>61400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>899200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1104300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>562000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>469600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>524600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>466200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>520900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>104900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>459100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>296700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>420600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>808500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>607500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4522400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5346400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5234800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5056500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5039100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2070100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2078600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2421700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2237200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2800500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3465400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3212200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3052900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3012300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3038300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3069700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3104300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3400300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3241800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3468900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3037000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3430300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3521600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3324300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3377200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3392600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6088100</v>
+      </c>
+      <c r="E46" s="3">
         <v>6129900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5670400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6213500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4794400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5490100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8095200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5134100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5999900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6170700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7022800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6069600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5551600</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4847,365 +4949,377 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1373300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1364900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1247300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1232100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1250200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1205700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1162800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1117700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1107300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1058600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1011200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>968500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>914200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3067400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3630300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3732400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3859700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2994700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1443300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1506000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1578100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1545700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1631300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1728600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1276600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1222600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1247600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1187800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1181300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1194400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1194800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1214800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1193300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>1141100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>1120600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>974200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>916700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>898000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>36800</v>
+      </c>
+      <c r="E48" s="3">
         <v>39400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>38800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>61000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>66500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>57000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>60700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>75800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>55302800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>54751400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>54433800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>54686500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>57946300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>34465600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>34797100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>34626000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>35219600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>34799600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>35422400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>35738700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35940500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>35303800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>35329900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>35159700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>35081500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>33215800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>32977000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>32187700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>32427900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>31610400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>30993100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>31595700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>31538400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>30913200</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1803100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1895600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2003200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2153400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2263200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2403300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2566600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2698900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2894400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3045200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3176900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3310800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3494300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3549700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3800700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3974100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4118300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4653400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>802300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>828200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>850000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>874500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>912900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1031500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1076100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1117000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1230000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1276200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1381400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1441800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1528600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1617300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1734900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1857400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2036700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2205600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2415900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2565000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2832800</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5323,8 +5437,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5442,127 +5559,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>61948700</v>
+      </c>
+      <c r="E52" s="3">
         <v>62069100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62713300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63732400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63941200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>62036000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61659400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>61816200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>60766400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>60667400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>60120700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>59302700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>59433700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>662800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>267800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>347200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>439800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>611900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>537500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>368000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>399900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>378100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>390400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>513200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>626300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>610600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1113800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>846300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1002600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>533400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>827300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>656000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1076900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>747400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1176500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>735900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>652000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>930500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5680,127 +5803,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71421400</v>
+      </c>
+      <c r="E54" s="3">
         <v>71671800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71938300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73633900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72555500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71442000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>73824900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>71106700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>71105000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>71274600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>71593700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>69928400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>69684400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>69726900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>69811200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>69747600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>70208200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>74569800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41499300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41824100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>42065000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>42048000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>44421100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>45193800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>47144800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43749200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>43549000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>43067900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>44717000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>43208900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>42149500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>42019400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>42493700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>42040100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>41006700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41019500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>41442900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>41620500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>41797800</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5842,8 +5971,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5885,169 +6015,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>519100</v>
+      </c>
+      <c r="E57" s="3">
         <v>562800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>527000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>488000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>478600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>465700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>423300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>420600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>429400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>444000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>430000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>475300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>582000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>475200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>711100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>730700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>750800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>850200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>263600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>281300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>243700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>222200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>223100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>220100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>240400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>239100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>233400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>245800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>272000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>294300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>274900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>283900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>303900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>307400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>288100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>295500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>302400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>330400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>276700</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E58" s="3">
         <v>97200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>78100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>95200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>63600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>80500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>54200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>64000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>80800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>44500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>62500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6078,23 +6212,23 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-      <c r="AA58" s="3" t="s">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>9000</v>
-      </c>
-      <c r="AF58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG58" s="3" t="s">
         <v>8</v>
@@ -6105,8 +6239,8 @@
       <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>0</v>
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK58" s="3">
         <v>0</v>
@@ -6123,8 +6257,11 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6164,128 +6301,131 @@
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3782000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3535700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3578300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3512900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4200400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2329700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2566800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2650700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2670700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2697700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2876000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3186500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3244500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3336800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3326300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3413000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3268700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3363100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3314500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3492500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3544100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3690200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3806900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3878800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3896900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4100200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4588300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4566400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4478500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4454100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4300900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4216600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4084000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3848600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3889600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3737200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3530100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3400800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3480500</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6361,246 +6501,255 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>43078400</v>
+      </c>
+      <c r="E61" s="3">
         <v>43589800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>44077200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46156400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46229000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>45350300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>48418000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45759800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45785300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>46576000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>47581200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>46343800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>46381700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>46533000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>47350100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47927900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>48912900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>50204700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>27539700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>28098600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>28553100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>28742100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>31087100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>30683900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>32760800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>29474500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>29280000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>29014200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>30750100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>29507600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>28387500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>28545500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>28890300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>28420700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>27287600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>27181000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>27520500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>27717000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>27997900</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1244900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1185000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1154400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1207400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1144300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1092600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1050400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1007900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1063100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1018700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>945900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>876600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>845000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2194100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1925700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1859500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1807600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2085200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1054900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>996000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>954000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>913400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>884100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>990300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>950200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>910300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>935800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>892200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>842100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>804600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>789900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>750500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>712400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>673900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>685900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>655900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>615300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>579000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>474100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6718,8 +6867,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6837,8 +6989,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6956,127 +7111,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53023700</v>
+      </c>
+      <c r="E66" s="3">
         <v>53348300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53788900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>55686700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>55363200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>54257100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>57072400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>54090200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54149200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>54685500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>55221500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>53537900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>53560800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>53609400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54243500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>54713200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>55555100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57999000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31644400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>32440600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>32925600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>33183600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>35609700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>35559800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>37761900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>34434300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>34374100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>34054900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>35810800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>34380900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>33279700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>33349900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>33901100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33460400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>32460300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>32498700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>32923200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>33096000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>33428300</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7118,8 +7279,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7237,8 +7399,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7356,8 +7521,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7475,8 +7643,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7594,127 +7765,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17071600</v>
+      </c>
+      <c r="E72" s="3">
         <v>16320600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15730700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14563600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13351300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12755800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>12129400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11802200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11407200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10802600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9703300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8598000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8104800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7674900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7181000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6741800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6408100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8410300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8322600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7888700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7625700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7399700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7380700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8232500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7986100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7734600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7424100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7157200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6825300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6591700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6359700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6096000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5846500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5580300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5313100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5047300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4767400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4509000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4147000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7832,8 +8009,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7951,8 +8131,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8070,127 +8253,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18397500</v>
+      </c>
+      <c r="E76" s="3">
         <v>18323300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18149200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17947100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17192100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17184600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16752300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17016200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16955600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16588800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16293700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16311900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16045400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16117500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15567700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15034400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14653100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16570700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9855000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9383500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9139300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8864500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8811400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>9634000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>9382900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>9314900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>9174900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>9013000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8906200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8828000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>8869900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>8669500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8592600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>8579700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>8546500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>8520800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>8519700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>8524400</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>8369500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8308,251 +8497,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>818100</v>
+      </c>
+      <c r="E81" s="3">
         <v>632800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1215700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1259200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>642900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>671200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>375000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>448200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>604200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1105800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1105300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>492900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>432100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>495000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>440000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>339800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2000800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>88800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>433900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>249800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>228000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>28500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-849900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>246100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>276800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>309800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>270300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>331500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>234200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>232600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>263400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>254200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>265400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>266300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>265800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>282900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>261200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>364700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>225600</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8594,127 +8792,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>593700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>580900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>580700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>634400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>555800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>393400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>392200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>396600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>401800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>416000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>411800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>415800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>415900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>415300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>419100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>425800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>428500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>415300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>422100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>425500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>428200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>431000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>438900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>442800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>438200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>444600</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8832,8 +9034,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8951,8 +9156,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9070,8 +9278,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9189,8 +9400,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9308,127 +9522,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1431700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1220500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1506200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1331400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1335000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1284300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1367800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1408800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1375700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1399600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1305200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1193200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1363400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1550600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1111900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1171900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1336600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1734500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>787800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>771200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>400400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>652500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>541000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>307900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>628900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>768300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>817100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>774500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>745700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>778400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>716700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>607300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>738000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>724300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>817200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>797200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>801500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>935200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>831100</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9470,127 +9690,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1501600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2082000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1021400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-470100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2500800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1627800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1733700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1623400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1631500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1572800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1338700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1740700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-944700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1183100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-685000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1058800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-975800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-312900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-11000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-99100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-146100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-98600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-354100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-436100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-298900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-280300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-406700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-637200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-420300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-325800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-366900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-308500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-870900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1424200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-856500</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9708,8 +9932,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9827,127 +10054,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-183200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-916300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>550800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>706200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2005200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-659200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1372600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-850700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-841800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-628600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-303100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-973200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1278100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-453600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-844200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-216100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-646600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23038300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-187300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-302600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>69300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-220800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>70000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-326200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-235200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-714600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-910900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-546100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-783200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1737800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1073100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-718900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-522900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1447000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-893300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-608400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-478700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-774500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9989,34 +10222,35 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E96" s="3">
         <v>50700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>46400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>89800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>5600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>50200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>48000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>41800</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
@@ -10030,8 +10264,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10108,8 +10342,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10227,8 +10464,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10346,8 +10586,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10465,361 +10708,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1146600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-736700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2990200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-460600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>534500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3172800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2344500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-431600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-872700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1554600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>289000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-166500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-579700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-600300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-403700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-897800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1259100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>21683500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-660400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-550600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-288700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2463400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>270100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2221500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3189500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>48700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>321700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1832400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1197100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>965800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-93700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-484500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>212800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>928800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-70800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-522900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-422700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-352100</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1274100</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="S101" s="3">
-        <v>500</v>
       </c>
       <c r="T101" s="3">
         <v>500</v>
       </c>
       <c r="U101" s="3">
+        <v>500</v>
+      </c>
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-700</v>
       </c>
-      <c r="AK101" s="3">
-        <v>0</v>
-      </c>
       <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
         <v>-400</v>
       </c>
-      <c r="AM101" s="3">
-        <v>0</v>
-      </c>
       <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-432700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-933700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1576900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-132300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2552900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2342300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>126700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-340000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-781200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1289700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-493100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-145700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>56200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-568500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>380200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-58900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-82100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>180200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2030500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>882700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2239400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3582200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>103700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>226300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1603900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1159200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-449700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-593700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>428000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>205400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-146800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-334600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-99800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-192600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-356500</v>
       </c>
     </row>
